--- a/Belle2/data.xlsx
+++ b/Belle2/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\Belle2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BB4799-6532-474B-BA13-09DA0CDC4F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D121037-724B-4908-BB7D-0B2D0A426BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,22 +349,22 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.71235400000000004</v>
+        <v>0.81627099999999997</v>
       </c>
       <c r="B1">
-        <v>0.20435400000000001</v>
+        <v>0.150508</v>
       </c>
       <c r="C1">
-        <v>5.7730000000000004E-3</v>
+        <v>3.3899999999999998E-3</v>
       </c>
       <c r="D1">
-        <v>1.8140000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="E1">
-        <v>6.6E-4</v>
+        <v>0</v>
       </c>
       <c r="F1">
-        <v>1.3190000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="G1">
         <v>0</v>
@@ -379,16 +379,16 @@
         <v>0</v>
       </c>
       <c r="K1">
-        <v>1.65E-4</v>
+        <v>0</v>
       </c>
       <c r="L1">
-        <v>3.1503000000000003E-2</v>
+        <v>1.3559E-2</v>
       </c>
       <c r="M1">
-        <v>1.65E-4</v>
+        <v>0</v>
       </c>
       <c r="N1">
-        <v>4.4530000000000004E-3</v>
+        <v>6.78E-4</v>
       </c>
       <c r="O1">
         <v>0</v>
@@ -406,33 +406,33 @@
         <v>0</v>
       </c>
       <c r="T1">
-        <v>1.65E-4</v>
+        <v>0</v>
       </c>
       <c r="U1">
-        <v>3.7275000000000003E-2</v>
+        <v>1.5592999999999999E-2</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>4.0670999999999999E-2</v>
+        <v>5.5275999999999999E-2</v>
       </c>
       <c r="B2">
-        <v>0.773289</v>
+        <v>0.78391999999999995</v>
       </c>
       <c r="C2">
-        <v>6.0460000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1.9239999999999999E-3</v>
+        <v>2.513E-3</v>
       </c>
       <c r="E2">
-        <v>5.7710000000000001E-3</v>
+        <v>1.005E-2</v>
       </c>
       <c r="F2">
-        <v>6.3200000000000001E-3</v>
+        <v>2.513E-3</v>
       </c>
       <c r="G2">
-        <v>2.7500000000000002E-4</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -447,25 +447,25 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1.1816E-2</v>
+        <v>1.5075E-2</v>
       </c>
       <c r="M2">
-        <v>1.0989999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.061E-2</v>
+        <v>7.5380000000000004E-3</v>
       </c>
       <c r="O2">
-        <v>2.7500000000000002E-4</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>8.2399999999999997E-4</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2.7500000000000002E-4</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -474,30 +474,30 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.130805</v>
+        <v>0.123116</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>5.1000000000000004E-4</v>
+        <v>3.5839999999999999E-3</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.82763900000000001</v>
+        <v>0.92114700000000005</v>
       </c>
       <c r="D3">
-        <v>2.0400000000000001E-3</v>
+        <v>3.5839999999999999E-3</v>
       </c>
       <c r="E3">
-        <v>0.11677700000000001</v>
+        <v>6.0932E-2</v>
       </c>
       <c r="F3">
-        <v>5.1000000000000004E-4</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1.5299999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -509,25 +509,25 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>5.6090000000000003E-3</v>
+        <v>7.1679999999999999E-3</v>
       </c>
       <c r="L3">
-        <v>5.1000000000000004E-4</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>7.6490000000000004E-3</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>8.6689999999999996E-3</v>
+        <v>3.5839999999999999E-3</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>5.6090000000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -539,60 +539,60 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.2946999999999999E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>6.0099999999999997E-4</v>
+        <v>0</v>
       </c>
       <c r="B4">
-        <v>4.8079999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>9.0139999999999994E-3</v>
+        <v>1.5873000000000002E-2</v>
       </c>
       <c r="D4">
-        <v>0.579928</v>
+        <v>0.730159</v>
       </c>
       <c r="E4">
-        <v>1.2019999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0.241587</v>
+        <v>0.19047600000000001</v>
       </c>
       <c r="G4">
-        <v>3.6059999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.0099999999999997E-4</v>
+        <v>5.2909999999999997E-3</v>
       </c>
       <c r="I4">
-        <v>1.2019999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>6.0099999999999997E-4</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>1.2019999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>2.8846E-2</v>
+        <v>1.5873000000000002E-2</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>2.1635000000000001E-2</v>
+        <v>1.0581999999999999E-2</v>
       </c>
       <c r="O4">
-        <v>6.0099999999999997E-4</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1.4423E-2</v>
+        <v>5.2909999999999997E-3</v>
       </c>
       <c r="Q4">
-        <v>6.0099999999999997E-4</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -604,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8.9542999999999998E-2</v>
+        <v>2.6454999999999999E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
@@ -615,19 +615,19 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.19806799999999999</v>
+        <v>0.25</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.57246399999999997</v>
+        <v>0.5625</v>
       </c>
       <c r="F5">
-        <v>2.415E-3</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>2.415E-3</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -639,25 +639,25 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>2.415E-3</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>1.4493000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>2.415E-3</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>2.4154999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.6907999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.16425100000000001</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.45">
@@ -677,19 +677,19 @@
         <v>0</v>
       </c>
       <c r="B6">
-        <v>4.7060000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>7.0587999999999998E-2</v>
+        <v>0.111111</v>
       </c>
       <c r="E6">
-        <v>2.3530000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0.55529399999999995</v>
+        <v>0.61111099999999996</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -707,22 +707,22 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>1.1764999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>2.8235E-2</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>2.3530000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>7.0590000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.3530000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.31529400000000002</v>
+        <v>0.27777800000000002</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.45">
@@ -745,19 +745,19 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>1.5625E-2</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1.5625E-2</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.328125</v>
+        <v>0.33333299999999999</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -778,16 +778,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.5625E-2</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>1.5625E-2</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>9.375E-2</v>
+        <v>0</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.515625</v>
+        <v>0.66666700000000001</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.45">
@@ -807,31 +807,31 @@
         <v>0</v>
       </c>
       <c r="B8">
-        <v>1.1110999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>2.2221999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>1.1110999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>8.8888999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -858,13 +858,13 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>4.4443999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>2.2221999999999999E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.45">
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.45">
@@ -955,13 +955,13 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0.14285700000000001</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0.71428599999999998</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.14285700000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.45">
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>8.4125000000000005E-2</v>
+        <v>2.6315999999999999E-2</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>9.4979999999999995E-3</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0.654003</v>
+        <v>0.78947400000000001</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0.19403000000000001</v>
+        <v>0.16447400000000001</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.3569999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1059,63 +1059,63 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>5.6987999999999997E-2</v>
+        <v>1.9737000000000001E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>2.075E-3</v>
+        <v>1.157E-3</v>
       </c>
       <c r="B12">
-        <v>4.4099999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>2.3349999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>2.1530000000000001E-2</v>
+        <v>8.1019999999999998E-3</v>
       </c>
       <c r="E12">
-        <v>5.1900000000000004E-4</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>8.8199999999999997E-3</v>
+        <v>1.157E-3</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>2.5900000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>5.1900000000000004E-4</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>1.5560000000000001E-3</v>
+        <v>2.3149999999999998E-3</v>
       </c>
       <c r="L12">
-        <v>0.81789900000000004</v>
+        <v>0.89583299999999999</v>
       </c>
       <c r="M12">
-        <v>2.5900000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>0.114916</v>
+        <v>8.3333000000000004E-2</v>
       </c>
       <c r="O12">
-        <v>3.372E-3</v>
+        <v>1.157E-3</v>
       </c>
       <c r="P12">
-        <v>1.0380000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.5900000000000001E-4</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>5.1900000000000004E-4</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1.9715E-2</v>
+        <v>6.9439999999999997E-3</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.45">
@@ -1132,16 +1132,16 @@
         <v>0</v>
       </c>
       <c r="B13">
-        <v>1.908E-3</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>3.2443E-2</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>3.4351E-2</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1159,16 +1159,16 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>6.2977000000000005E-2</v>
+        <v>8.1081E-2</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0.70801499999999995</v>
+        <v>0.81081099999999995</v>
       </c>
       <c r="N13">
-        <v>1.908E-3</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>1.908E-3</v>
+        <v>0</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.15648899999999999</v>
+        <v>0.108108</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.45">
@@ -1197,25 +1197,25 @@
         <v>0</v>
       </c>
       <c r="B14">
-        <v>4.3909999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>2.1949999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>1.3172E-2</v>
+        <v>9.5239999999999995E-3</v>
       </c>
       <c r="E14">
-        <v>1.098E-3</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>3.7322000000000001E-2</v>
+        <v>1.9047999999999999E-2</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>1.098E-3</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1224,28 +1224,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>1.098E-3</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>0.12842999999999999</v>
+        <v>0.15238099999999999</v>
       </c>
       <c r="M14">
-        <v>4.3909999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>0.61909999999999998</v>
+        <v>0.72380999999999995</v>
       </c>
       <c r="O14">
-        <v>6.5859999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>1.098E-3</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>1.0977000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>1.098E-3</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>0.16794700000000001</v>
+        <v>9.5238000000000003E-2</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.45">
@@ -1265,19 +1265,19 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>2.5773000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>5.1549999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>2.5773000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1292,22 +1292,22 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>5.1549999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>5.1549999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>5.1549999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>0.59793799999999997</v>
+        <v>0.76190500000000005</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0.22164900000000001</v>
+        <v>0.14285700000000001</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>0.108247</v>
+        <v>9.5238000000000003E-2</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.45">
@@ -1333,13 +1333,13 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>4.1667000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>3.4722000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>6.9439999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1357,25 +1357,25 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>1.3889E-2</v>
+        <v>0</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
       <c r="N16">
-        <v>1.3889E-2</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>2.0833000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>0.36805599999999999</v>
+        <v>0.63636400000000004</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
       <c r="R16">
-        <v>1.3889E-2</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0.48611100000000002</v>
+        <v>0.36363600000000001</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.45">
@@ -1395,19 +1395,19 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>1.5625E-2</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>3.125E-2</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>1.5625E-2</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>1.5625E-2</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1428,16 +1428,16 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>1.5625E-2</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.125E-2</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0.5625</v>
+        <v>0</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>0.3125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.45">
@@ -1505,16 +1505,16 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>0.72727299999999995</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="T18">
-        <v>9.0909000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>0.18181800000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.45">
@@ -1573,13 +1573,13 @@
         <v>0</v>
       </c>
       <c r="S19">
-        <v>0.83333299999999999</v>
+        <v>0</v>
       </c>
       <c r="T19">
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0.16666700000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.45">
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Belle2/data.xlsx
+++ b/Belle2/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\Belle2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D121037-724B-4908-BB7D-0B2D0A426BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BC4EEA-4389-4518-94E8-57B845B649E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,22 +349,22 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.81627099999999997</v>
+        <v>0.73900999999999994</v>
       </c>
       <c r="B1">
-        <v>0.150508</v>
+        <v>0.19405900000000001</v>
       </c>
       <c r="C1">
-        <v>3.3899999999999998E-3</v>
+        <v>4.3559999999999996E-3</v>
       </c>
       <c r="D1">
-        <v>0</v>
+        <v>2.3760000000000001E-3</v>
       </c>
       <c r="E1">
         <v>0</v>
       </c>
       <c r="F1">
-        <v>0</v>
+        <v>1.5839999999999999E-3</v>
       </c>
       <c r="G1">
         <v>0</v>
@@ -379,16 +379,16 @@
         <v>0</v>
       </c>
       <c r="K1">
-        <v>0</v>
+        <v>3.9599999999999998E-4</v>
       </c>
       <c r="L1">
-        <v>1.3559E-2</v>
+        <v>3.2079000000000003E-2</v>
       </c>
       <c r="M1">
         <v>0</v>
       </c>
       <c r="N1">
-        <v>6.78E-4</v>
+        <v>5.1489999999999999E-3</v>
       </c>
       <c r="O1">
         <v>0</v>
@@ -409,27 +409,27 @@
         <v>0</v>
       </c>
       <c r="U1">
-        <v>1.5592999999999999E-2</v>
+        <v>2.0990000000000002E-2</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>5.5275999999999999E-2</v>
+        <v>5.1382999999999998E-2</v>
       </c>
       <c r="B2">
-        <v>0.78391999999999995</v>
+        <v>0.79130400000000001</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>8.6960000000000006E-3</v>
       </c>
       <c r="D2">
-        <v>2.513E-3</v>
+        <v>3.9529999999999999E-3</v>
       </c>
       <c r="E2">
-        <v>1.005E-2</v>
+        <v>1.5809999999999999E-3</v>
       </c>
       <c r="F2">
-        <v>2.513E-3</v>
+        <v>4.7429999999999998E-3</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -441,22 +441,22 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>7.9100000000000004E-4</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1.5075E-2</v>
+        <v>1.1067E-2</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>7.5380000000000004E-3</v>
+        <v>1.8971999999999999E-2</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>7.9100000000000004E-4</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -474,24 +474,24 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.123116</v>
+        <v>0.10671899999999999</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>3.5839999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.92114700000000005</v>
+        <v>0.83759399999999995</v>
       </c>
       <c r="D3">
-        <v>3.5839999999999999E-3</v>
+        <v>1.5039999999999999E-3</v>
       </c>
       <c r="E3">
-        <v>6.0932E-2</v>
+        <v>0.12781999999999999</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -509,25 +509,25 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>7.1679999999999999E-3</v>
+        <v>3.0079999999999998E-3</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>4.5110000000000003E-3</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1.5039999999999999E-3</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>3.5839999999999999E-3</v>
+        <v>1.2030000000000001E-2</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.5039999999999999E-3</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.0526000000000001E-2</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.45">
@@ -547,28 +547,28 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>3.509E-3</v>
       </c>
       <c r="C4">
-        <v>1.5873000000000002E-2</v>
+        <v>1.4035000000000001E-2</v>
       </c>
       <c r="D4">
-        <v>0.730159</v>
+        <v>0.64736800000000005</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.19047600000000001</v>
+        <v>0.221053</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>5.2909999999999997E-3</v>
+        <v>1.7539999999999999E-3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1.7539999999999999E-3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -577,22 +577,22 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.5873000000000002E-2</v>
+        <v>2.4560999999999999E-2</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.0581999999999999E-2</v>
+        <v>5.2630000000000003E-3</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>5.2909999999999997E-3</v>
+        <v>1.2281E-2</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.7539999999999999E-3</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -604,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.6454999999999999E-2</v>
+        <v>6.6667000000000004E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
@@ -615,19 +615,19 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.25</v>
+        <v>0.20547899999999999</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.5625</v>
+        <v>0.58219200000000004</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1.3698999999999999E-2</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -642,22 +642,22 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>6.8490000000000001E-3</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>2.0548E-2</v>
       </c>
       <c r="N5">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.0548E-2</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.0548E-2</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.1875</v>
+        <v>0.130137</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.45">
@@ -677,19 +677,19 @@
         <v>0</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>7.2459999999999998E-3</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.111111</v>
+        <v>8.6957000000000007E-2</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>7.2459999999999998E-3</v>
       </c>
       <c r="F6">
-        <v>0.61111099999999996</v>
+        <v>0.65942000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -707,19 +707,19 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>7.2459999999999998E-3</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>5.7971000000000002E-2</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>7.2459999999999998E-3</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.27777800000000002</v>
+        <v>0.16666700000000001</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.45">
@@ -781,13 +781,13 @@
         <v>0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>6.6667000000000004E-2</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>6.6667000000000004E-2</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.66666700000000001</v>
+        <v>0.53333299999999995</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.45">
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>4.8779999999999997E-2</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -825,13 +825,13 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.82926800000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>0.121951</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>2.6315999999999999E-2</v>
+        <v>8.1559999999999994E-2</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1.0638E-2</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0.78947400000000001</v>
+        <v>0.62766</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0.16447400000000001</v>
+        <v>0.25531900000000002</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1059,27 +1059,27 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1.9737000000000001E-2</v>
+        <v>2.4823000000000001E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>1.157E-3</v>
+        <v>0</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>2.0630000000000002E-3</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1.3760000000000001E-3</v>
       </c>
       <c r="D12">
-        <v>8.1019999999999998E-3</v>
+        <v>1.7881999999999999E-2</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>6.8800000000000003E-4</v>
       </c>
       <c r="F12">
-        <v>1.157E-3</v>
+        <v>1.238E-2</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1094,19 +1094,19 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>2.3149999999999998E-3</v>
+        <v>1.3760000000000001E-3</v>
       </c>
       <c r="L12">
-        <v>0.89583299999999999</v>
+        <v>0.842503</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.3760000000000001E-3</v>
       </c>
       <c r="N12">
-        <v>8.3333000000000004E-2</v>
+        <v>0.101788</v>
       </c>
       <c r="O12">
-        <v>1.157E-3</v>
+        <v>2.751E-3</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>6.9439999999999997E-3</v>
+        <v>1.5817999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.45">
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>3.8674E-2</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>4.4199000000000002E-2</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1159,19 +1159,19 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>8.1081E-2</v>
+        <v>6.0773000000000001E-2</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0.81081099999999995</v>
+        <v>0.74033099999999996</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>5.5250000000000004E-3</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.108108</v>
+        <v>0.110497</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.45">
@@ -1197,19 +1197,19 @@
         <v>0</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>8.9549999999999994E-3</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2.9849999999999998E-3</v>
       </c>
       <c r="D14">
-        <v>9.5239999999999995E-3</v>
+        <v>2.0896000000000001E-2</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2.9849999999999998E-3</v>
       </c>
       <c r="F14">
-        <v>1.9047999999999999E-2</v>
+        <v>3.2835999999999997E-2</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1224,19 +1224,19 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>2.9849999999999998E-3</v>
       </c>
       <c r="L14">
-        <v>0.15238099999999999</v>
+        <v>0.14029900000000001</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>5.9699999999999996E-3</v>
       </c>
       <c r="N14">
-        <v>0.72380999999999995</v>
+        <v>0.66268700000000003</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>2.9849999999999998E-3</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>9.5238000000000003E-2</v>
+        <v>0.11641799999999999</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.45">
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1.5152000000000001E-2</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1292,22 +1292,22 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.5152000000000001E-2</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.5152000000000001E-2</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.5152000000000001E-2</v>
       </c>
       <c r="O15">
-        <v>0.76190500000000005</v>
+        <v>0.5</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.5152000000000001E-2</v>
       </c>
       <c r="Q15">
-        <v>0.14285700000000001</v>
+        <v>0.34848499999999999</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>9.5238000000000003E-2</v>
+        <v>7.5758000000000006E-2</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.45">
@@ -1339,10 +1339,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2.3810000000000001E-2</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2.3810000000000001E-2</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1363,13 +1363,13 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.3810000000000001E-2</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0.63636400000000004</v>
+        <v>0.33333299999999999</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0.36363600000000001</v>
+        <v>0.59523800000000004</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.45">
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>7.6923000000000005E-2</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1431,13 +1431,13 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>0.15384600000000001</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>0.538462</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>1</v>
+        <v>0.230769</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.45">
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19">
         <v>0</v>

--- a/Belle2/data.xlsx
+++ b/Belle2/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\Belle2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BC4EEA-4389-4518-94E8-57B845B649E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1F2FAF-4072-4C0A-B3F0-8FDC4996EC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,22 +349,22 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.73900999999999994</v>
+        <v>0.80368099999999998</v>
       </c>
       <c r="B1">
-        <v>0.19405900000000001</v>
+        <v>0.157975</v>
       </c>
       <c r="C1">
-        <v>4.3559999999999996E-3</v>
+        <v>7.6689999999999996E-3</v>
       </c>
       <c r="D1">
-        <v>2.3760000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="E1">
         <v>0</v>
       </c>
       <c r="F1">
-        <v>1.5839999999999999E-3</v>
+        <v>7.67E-4</v>
       </c>
       <c r="G1">
         <v>0</v>
@@ -379,16 +379,16 @@
         <v>0</v>
       </c>
       <c r="K1">
-        <v>3.9599999999999998E-4</v>
+        <v>0</v>
       </c>
       <c r="L1">
-        <v>3.2079000000000003E-2</v>
+        <v>1.1502999999999999E-2</v>
       </c>
       <c r="M1">
         <v>0</v>
       </c>
       <c r="N1">
-        <v>5.1489999999999999E-3</v>
+        <v>2.3010000000000001E-3</v>
       </c>
       <c r="O1">
         <v>0</v>
@@ -409,27 +409,27 @@
         <v>0</v>
       </c>
       <c r="U1">
-        <v>2.0990000000000002E-2</v>
+        <v>1.6104E-2</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>5.1382999999999998E-2</v>
+        <v>6.8825999999999998E-2</v>
       </c>
       <c r="B2">
-        <v>0.79130400000000001</v>
+        <v>0.85829999999999995</v>
       </c>
       <c r="C2">
-        <v>8.6960000000000006E-3</v>
+        <v>2.0243000000000001E-2</v>
       </c>
       <c r="D2">
-        <v>3.9529999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1.5809999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>4.7429999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -441,22 +441,22 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>7.9100000000000004E-4</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1.1067E-2</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.8971999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>7.9100000000000004E-4</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.10671899999999999</v>
+        <v>5.2631999999999998E-2</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
@@ -485,13 +485,13 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.83759399999999995</v>
+        <v>0.91025599999999995</v>
       </c>
       <c r="D3">
-        <v>1.5039999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0.12781999999999999</v>
+        <v>7.2650000000000006E-2</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -509,25 +509,25 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3.0079999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>4.5110000000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.5039999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>1.2030000000000001E-2</v>
+        <v>4.274E-3</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.5039999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.0526000000000001E-2</v>
+        <v>1.2821000000000001E-2</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.45">
@@ -547,28 +547,28 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>3.509E-3</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1.4035000000000001E-2</v>
+        <v>2.3973000000000001E-2</v>
       </c>
       <c r="D4">
-        <v>0.64736800000000005</v>
+        <v>0.71917799999999998</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.221053</v>
+        <v>0.188356</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3.4250000000000001E-3</v>
       </c>
       <c r="H4">
-        <v>1.7539999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>1.7539999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -577,22 +577,22 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>2.4560999999999999E-2</v>
+        <v>6.8490000000000001E-3</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>5.2630000000000003E-3</v>
+        <v>3.4250000000000001E-3</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.2281E-2</v>
+        <v>1.7122999999999999E-2</v>
       </c>
       <c r="Q4">
-        <v>1.7539999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -604,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>6.6667000000000004E-2</v>
+        <v>3.7671000000000003E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
@@ -615,19 +615,19 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.20547899999999999</v>
+        <v>0.14285700000000001</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.58219200000000004</v>
+        <v>0.71428599999999998</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1.3698999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -642,22 +642,22 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>6.8490000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>2.0548E-2</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>2.0548E-2</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.0548E-2</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.130137</v>
+        <v>0.14285700000000001</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.45">
@@ -677,19 +677,19 @@
         <v>0</v>
       </c>
       <c r="B6">
-        <v>7.2459999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>8.6957000000000007E-2</v>
+        <v>0.18181800000000001</v>
       </c>
       <c r="E6">
-        <v>7.2459999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0.65942000000000001</v>
+        <v>0.77272700000000005</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -707,19 +707,19 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>7.2459999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>5.7971000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>7.2459999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.16666700000000001</v>
+        <v>4.5455000000000002E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.45">
@@ -757,7 +757,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.33333299999999999</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -781,13 +781,13 @@
         <v>0</v>
       </c>
       <c r="O7">
-        <v>6.6667000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>6.6667000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.53333299999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.45">
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>4.8779999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -825,13 +825,13 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.82926800000000001</v>
+        <v>0.92857100000000004</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0.121951</v>
+        <v>7.1429000000000006E-2</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>8.1559999999999994E-2</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>1.0638E-2</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0.62766</v>
+        <v>0.80821900000000002</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0.25531900000000002</v>
+        <v>0.164384</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>2.4823000000000001E-2</v>
+        <v>2.7397000000000001E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.45">
@@ -1067,19 +1067,19 @@
         <v>0</v>
       </c>
       <c r="B12">
-        <v>2.0630000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1.3760000000000001E-3</v>
+        <v>1.1919999999999999E-3</v>
       </c>
       <c r="D12">
-        <v>1.7881999999999999E-2</v>
+        <v>5.9589999999999999E-3</v>
       </c>
       <c r="E12">
-        <v>6.8800000000000003E-4</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>1.238E-2</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1094,19 +1094,19 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>1.3760000000000001E-3</v>
+        <v>2.3839999999999998E-3</v>
       </c>
       <c r="L12">
-        <v>0.842503</v>
+        <v>0.91656700000000002</v>
       </c>
       <c r="M12">
-        <v>1.3760000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>0.101788</v>
+        <v>6.1978999999999999E-2</v>
       </c>
       <c r="O12">
-        <v>2.751E-3</v>
+        <v>1.1919999999999999E-3</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1.5817999999999999E-2</v>
+        <v>1.0727E-2</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.45">
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>3.8674E-2</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>4.4199000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1159,19 +1159,19 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>6.0773000000000001E-2</v>
+        <v>6.4516000000000004E-2</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0.74033099999999996</v>
+        <v>0.80645199999999995</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="O13">
-        <v>5.5250000000000004E-3</v>
+        <v>0</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.110497</v>
+        <v>0.12903200000000001</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.45">
@@ -1197,19 +1197,19 @@
         <v>0</v>
       </c>
       <c r="B14">
-        <v>8.9549999999999994E-3</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>2.9849999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>2.0896000000000001E-2</v>
+        <v>2.1739000000000001E-2</v>
       </c>
       <c r="E14">
-        <v>2.9849999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>3.2835999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1224,19 +1224,19 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>2.9849999999999998E-3</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>0.14029900000000001</v>
+        <v>0.23913000000000001</v>
       </c>
       <c r="M14">
-        <v>5.9699999999999996E-3</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>0.66268700000000003</v>
+        <v>0.69565200000000005</v>
       </c>
       <c r="O14">
-        <v>2.9849999999999998E-3</v>
+        <v>1.0869999999999999E-2</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>0.11641799999999999</v>
+        <v>3.2608999999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.45">
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>1.5152000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1292,22 +1292,22 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>1.5152000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>1.5152000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>1.5152000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>0.5</v>
+        <v>0.80952400000000002</v>
       </c>
       <c r="P15">
-        <v>1.5152000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>0.34848499999999999</v>
+        <v>0.19047600000000001</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>7.5758000000000006E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.45">
@@ -1339,10 +1339,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>2.3810000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>2.3810000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1363,13 +1363,13 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>2.3810000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0.33333299999999999</v>
+        <v>0.40909099999999998</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0.59523800000000004</v>
+        <v>0.59090900000000002</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.45">
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>7.6923000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1431,13 +1431,13 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>0.15384600000000001</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0.538462</v>
+        <v>0</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>0.230769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.45">
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19">
         <v>0</v>

--- a/Belle2/data.xlsx
+++ b/Belle2/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\Belle2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1F2FAF-4072-4C0A-B3F0-8FDC4996EC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56F97B2-97EB-4790-A308-B034B8E3904E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,22 +349,22 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.80368099999999998</v>
+        <v>0.52223399999999998</v>
       </c>
       <c r="B1">
-        <v>0.157975</v>
+        <v>0.36287799999999998</v>
       </c>
       <c r="C1">
-        <v>7.6689999999999996E-3</v>
+        <v>9.6819999999999996E-3</v>
       </c>
       <c r="D1">
-        <v>0</v>
+        <v>1.0449999999999999E-3</v>
       </c>
       <c r="E1">
-        <v>0</v>
+        <v>2.7659999999999998E-3</v>
       </c>
       <c r="F1">
-        <v>7.67E-4</v>
+        <v>1.0449999999999999E-3</v>
       </c>
       <c r="G1">
         <v>0</v>
@@ -379,25 +379,25 @@
         <v>0</v>
       </c>
       <c r="K1">
-        <v>0</v>
+        <v>1.4200000000000001E-4</v>
       </c>
       <c r="L1">
-        <v>1.1502999999999999E-2</v>
+        <v>1.3609E-2</v>
       </c>
       <c r="M1">
         <v>0</v>
       </c>
       <c r="N1">
-        <v>2.3010000000000001E-3</v>
+        <v>3.5950000000000001E-3</v>
       </c>
       <c r="O1">
-        <v>0</v>
+        <v>6.2000000000000003E-5</v>
       </c>
       <c r="P1">
         <v>0</v>
       </c>
       <c r="Q1">
-        <v>0</v>
+        <v>6.2000000000000003E-5</v>
       </c>
       <c r="R1">
         <v>0</v>
@@ -409,18 +409,18 @@
         <v>0</v>
       </c>
       <c r="U1">
-        <v>1.6104E-2</v>
+        <v>8.2879999999999995E-2</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>6.8825999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>0.85829999999999995</v>
+        <v>0.63654699999999997</v>
       </c>
       <c r="C2">
-        <v>2.0243000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -435,7 +435,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>5.9820000000000003E-3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -447,13 +447,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.7198999999999999E-2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.7198999999999999E-2</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>6.0330000000000002E-3</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.2631999999999998E-2</v>
+        <v>0.31703999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
@@ -485,13 +485,13 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.91025599999999995</v>
+        <v>0.77675700000000003</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7.2650000000000006E-2</v>
+        <v>0.17353299999999999</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -509,7 +509,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1.8389999999999999E-3</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -521,13 +521,13 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>4.274E-3</v>
+        <v>1.124E-2</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.606E-3</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.2821000000000001E-2</v>
+        <v>3.5025000000000001E-2</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.45">
@@ -550,19 +550,19 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>2.3973000000000001E-2</v>
+        <v>1.5533999999999999E-2</v>
       </c>
       <c r="D4">
-        <v>0.71917799999999998</v>
+        <v>0.57756300000000005</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.188356</v>
+        <v>0.30008600000000002</v>
       </c>
       <c r="G4">
-        <v>3.4250000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -577,19 +577,19 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>6.8490000000000001E-3</v>
+        <v>1.0056000000000001E-2</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>3.4250000000000001E-3</v>
+        <v>1.0364999999999999E-2</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.0730000000000002E-3</v>
       </c>
       <c r="P4">
-        <v>1.7122999999999999E-2</v>
+        <v>2.0730000000000002E-3</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -604,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3.7671000000000003E-2</v>
+        <v>8.2251000000000005E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
@@ -615,13 +615,13 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.14285700000000001</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.71428599999999998</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.14285700000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.45">
@@ -683,13 +683,13 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.18181800000000001</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.77272700000000005</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>4.5455000000000002E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.45">
@@ -757,49 +757,49 @@
         <v>0</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
         <v>1</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.45">
@@ -825,13 +825,13 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.92857100000000004</v>
+        <v>0.83313400000000004</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>7.1429000000000006E-2</v>
+        <v>8.3312999999999998E-2</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -858,13 +858,13 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.801E-2</v>
       </c>
       <c r="T8">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>5.5542000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.45">
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2.4445999999999999E-2</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>6.7390000000000002E-3</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0.80821900000000002</v>
+        <v>0.54363099999999998</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2.7680000000000001E-3</v>
       </c>
       <c r="M11">
-        <v>0.164384</v>
+        <v>0.34211799999999998</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1059,27 +1059,27 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>2.7397000000000001E-2</v>
+        <v>8.0298999999999995E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>0</v>
+        <v>3.0499999999999999E-4</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>9.2800000000000001E-4</v>
       </c>
       <c r="C12">
-        <v>1.1919999999999999E-3</v>
+        <v>9.9200000000000004E-4</v>
       </c>
       <c r="D12">
-        <v>5.9589999999999999E-3</v>
+        <v>6.2620000000000002E-3</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>2.5509999999999999E-3</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1094,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>2.3839999999999998E-3</v>
+        <v>1.6069999999999999E-3</v>
       </c>
       <c r="L12">
-        <v>0.91656700000000002</v>
+        <v>0.78740900000000003</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>6.6699999999999995E-4</v>
       </c>
       <c r="N12">
-        <v>6.1978999999999999E-2</v>
+        <v>0.16139600000000001</v>
       </c>
       <c r="O12">
-        <v>1.1919999999999999E-3</v>
+        <v>3.0409999999999999E-3</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.34E-4</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.34E-4</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>4.6799999999999999E-4</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1.0727E-2</v>
+        <v>3.3907E-2</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.45">
@@ -1159,13 +1159,13 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>6.4516000000000004E-2</v>
+        <v>0.14319999999999999</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0.80645199999999995</v>
+        <v>0.73173200000000005</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.12903200000000001</v>
+        <v>0.12506700000000001</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.45">
@@ -1197,13 +1197,13 @@
         <v>0</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>0.24839900000000001</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>2.1739000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1227,16 +1227,16 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0.23913000000000001</v>
+        <v>0</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14">
-        <v>0.69565200000000005</v>
+        <v>0.75160099999999996</v>
       </c>
       <c r="O14">
-        <v>1.0869999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>3.2608999999999999E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.45">
@@ -1301,13 +1301,13 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>0.80952400000000002</v>
+        <v>0.55555600000000005</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0.19047600000000001</v>
+        <v>0.296296</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>0.148148</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.45">
@@ -1354,10 +1354,10 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>4.5823000000000003E-2</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>0.11408699999999999</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -1366,16 +1366,16 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>4.0021000000000001E-2</v>
       </c>
       <c r="P16">
-        <v>0.40909099999999998</v>
+        <v>0.240123</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>4.0021000000000001E-2</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0.59090900000000002</v>
+        <v>0.519926</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.45">

--- a/Belle2/data.xlsx
+++ b/Belle2/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\Belle2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13ED01AC-3C2C-43F5-AC4A-DCD4871F5B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C13EA2-8994-4223-97B1-B3AD0F2A7ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -349,25 +349,25 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>0.55093199999999998</v>
+        <v>0.52534400000000003</v>
       </c>
       <c r="B1">
-        <v>0.33899899999999999</v>
+        <v>0.35337000000000002</v>
       </c>
       <c r="C1">
-        <v>1.6254999999999999E-2</v>
+        <v>1.7548999999999999E-2</v>
       </c>
       <c r="D1">
-        <v>2.8930000000000002E-3</v>
+        <v>3.1250000000000002E-3</v>
       </c>
       <c r="E1">
-        <v>1.946E-3</v>
+        <v>2.3549999999999999E-3</v>
       </c>
       <c r="F1">
-        <v>2.183E-3</v>
+        <v>2.4250000000000001E-3</v>
       </c>
       <c r="G1">
-        <v>2.5999999999999998E-5</v>
+        <v>4.6999999999999997E-5</v>
       </c>
       <c r="H1">
         <v>0</v>
@@ -376,90 +376,90 @@
         <v>0</v>
       </c>
       <c r="J1">
-        <v>1.2676E-2</v>
+        <v>1.4482999999999999E-2</v>
       </c>
       <c r="K1">
-        <v>5.3000000000000001E-5</v>
+        <v>6.9999999999999994E-5</v>
       </c>
       <c r="L1">
-        <v>1.3100000000000001E-4</v>
+        <v>1.63E-4</v>
       </c>
       <c r="M1">
-        <v>2.1000000000000001E-4</v>
+        <v>2.33E-4</v>
       </c>
       <c r="N1">
-        <v>7.8999999999999996E-5</v>
+        <v>9.2999999999999997E-5</v>
       </c>
       <c r="O1">
         <v>0</v>
       </c>
       <c r="P1">
-        <v>1.5200000000000001E-4</v>
+        <v>1.35E-4</v>
       </c>
       <c r="Q1">
-        <v>3.6083999999999998E-2</v>
+        <v>3.7516000000000001E-2</v>
       </c>
       <c r="R1">
-        <v>2.6999999999999999E-5</v>
+        <v>9.1000000000000003E-5</v>
       </c>
       <c r="S1">
-        <v>4.7219999999999996E-3</v>
+        <v>5.2919999999999998E-3</v>
       </c>
       <c r="T1">
-        <v>1.5899999999999999E-4</v>
+        <v>2.3499999999999999E-4</v>
       </c>
       <c r="U1">
-        <v>0</v>
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="V1">
-        <v>2.6999999999999999E-5</v>
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="W1">
-        <v>5.3000000000000001E-5</v>
+        <v>4.6999999999999997E-5</v>
       </c>
       <c r="X1">
         <v>0</v>
       </c>
       <c r="Y1">
-        <v>2.6999999999999999E-5</v>
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="Z1">
-        <v>1.8599999999999999E-4</v>
+        <v>2.5900000000000001E-4</v>
       </c>
       <c r="AA1">
         <v>0</v>
       </c>
       <c r="AB1">
-        <v>0</v>
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="AC1">
         <v>0</v>
       </c>
       <c r="AD1">
-        <v>0</v>
+        <v>4.6999999999999997E-5</v>
       </c>
       <c r="AE1">
-        <v>3.2181000000000001E-2</v>
+        <v>3.7026000000000003E-2</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>1.7243999999999999E-2</v>
+        <v>1.9060000000000001E-2</v>
       </c>
       <c r="B2">
-        <v>0.84068799999999999</v>
+        <v>0.82382299999999997</v>
       </c>
       <c r="C2">
-        <v>9.7090000000000006E-3</v>
+        <v>8.8350000000000008E-3</v>
       </c>
       <c r="D2">
-        <v>1.073E-3</v>
+        <v>2.2850000000000001E-3</v>
       </c>
       <c r="E2">
-        <v>4.7219999999999996E-3</v>
+        <v>5.1419999999999999E-3</v>
       </c>
       <c r="F2">
-        <v>2.3609999999999998E-3</v>
+        <v>1.523E-3</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -471,19 +471,19 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>5.8599999999999999E-2</v>
+        <v>6.3413999999999998E-2</v>
       </c>
       <c r="K2">
-        <v>2.1499999999999999E-4</v>
+        <v>5.71E-4</v>
       </c>
       <c r="L2">
-        <v>2.1499999999999999E-4</v>
+        <v>1.9000000000000001E-4</v>
       </c>
       <c r="M2">
-        <v>2.1499999999999999E-4</v>
+        <v>1.9000000000000001E-4</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.9000000000000001E-4</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -492,22 +492,22 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>6.0520000000000001E-3</v>
+        <v>6.1380000000000002E-3</v>
       </c>
       <c r="R2">
-        <v>1.0499999999999999E-3</v>
+        <v>1.8630000000000001E-3</v>
       </c>
       <c r="S2">
-        <v>1.1691E-2</v>
+        <v>1.2485E-2</v>
       </c>
       <c r="T2">
-        <v>2.1599999999999999E-4</v>
+        <v>1.92E-4</v>
       </c>
       <c r="U2">
         <v>0</v>
       </c>
       <c r="V2">
-        <v>2.1599999999999999E-4</v>
+        <v>1.92E-4</v>
       </c>
       <c r="W2">
         <v>0</v>
@@ -516,16 +516,16 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>2.1599999999999999E-4</v>
+        <v>1.92E-4</v>
       </c>
       <c r="Z2">
-        <v>6.4899999999999995E-4</v>
+        <v>5.7600000000000001E-4</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.92E-4</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -534,7 +534,7 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>4.4866000000000003E-2</v>
+        <v>5.2944999999999999E-2</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.45">
@@ -545,31 +545,31 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.881525</v>
+        <v>0.872201</v>
       </c>
       <c r="D3">
-        <v>2.4000000000000001E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="E3">
-        <v>9.7247E-2</v>
+        <v>0.103076</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>9.5799999999999998E-4</v>
+        <v>7.9900000000000001E-4</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>2.4000000000000001E-4</v>
+        <v>5.9900000000000003E-4</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2.8739999999999998E-3</v>
+        <v>4.3949999999999996E-3</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -584,25 +584,25 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>2.7659999999999998E-3</v>
+        <v>2.5379999999999999E-3</v>
       </c>
       <c r="Q3">
-        <v>7.2499999999999995E-4</v>
+        <v>6.0400000000000004E-4</v>
       </c>
       <c r="R3">
-        <v>3.068E-3</v>
+        <v>3.3349999999999999E-3</v>
       </c>
       <c r="S3">
-        <v>2.42E-4</v>
+        <v>2.0100000000000001E-4</v>
       </c>
       <c r="T3">
-        <v>4.5900000000000003E-3</v>
+        <v>4.8349999999999999E-3</v>
       </c>
       <c r="U3">
         <v>0</v>
       </c>
       <c r="V3">
-        <v>1.2080000000000001E-3</v>
+        <v>1.8129999999999999E-3</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -611,13 +611,13 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>2.0100000000000001E-4</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>2.42E-4</v>
+        <v>4.0299999999999998E-4</v>
       </c>
       <c r="AB3">
         <v>0</v>
@@ -629,51 +629,51 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>4.0759999999999998E-3</v>
+        <v>4.7990000000000003E-3</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>5.6800000000000004E-4</v>
+        <v>4.6200000000000001E-4</v>
       </c>
       <c r="B4">
-        <v>3.6939999999999998E-3</v>
+        <v>4.4089999999999997E-3</v>
       </c>
       <c r="C4">
-        <v>6.9560000000000004E-3</v>
+        <v>5.6569999999999997E-3</v>
       </c>
       <c r="D4">
-        <v>0.66210899999999995</v>
+        <v>0.64033899999999999</v>
       </c>
       <c r="E4">
-        <v>4.3199999999999998E-4</v>
+        <v>7.0200000000000004E-4</v>
       </c>
       <c r="F4">
-        <v>0.22919200000000001</v>
+        <v>0.23556299999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3.5100000000000002E-4</v>
       </c>
       <c r="H4">
-        <v>4.3199999999999998E-4</v>
+        <v>3.5100000000000002E-4</v>
       </c>
       <c r="I4">
-        <v>4.3199999999999998E-4</v>
+        <v>3.5100000000000002E-4</v>
       </c>
       <c r="J4">
-        <v>4.3199999999999998E-4</v>
+        <v>3.5100000000000002E-4</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.7697000000000001E-2</v>
+        <v>2.3872000000000001E-2</v>
       </c>
       <c r="M4">
-        <v>4.3199999999999998E-4</v>
+        <v>7.0200000000000004E-4</v>
       </c>
       <c r="N4">
-        <v>4.3199999999999998E-4</v>
+        <v>3.5100000000000002E-4</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -682,25 +682,25 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.9062999999999999E-2</v>
+        <v>3.0456E-2</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>1.1754000000000001E-2</v>
+        <v>1.3455E-2</v>
       </c>
       <c r="T4">
-        <v>4.35E-4</v>
+        <v>7.0799999999999997E-4</v>
       </c>
       <c r="U4">
-        <v>7.4009999999999996E-3</v>
+        <v>9.5600000000000008E-3</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>3.5399999999999999E-4</v>
       </c>
       <c r="W4">
-        <v>3.9179999999999996E-3</v>
+        <v>4.9569999999999996E-3</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>4.35E-4</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>0</v>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>2.4188999999999999E-2</v>
+        <v>2.7047000000000002E-2</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.45">
@@ -735,31 +735,31 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.181142</v>
+        <v>0.20831</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.64296900000000001</v>
+        <v>0.626946</v>
       </c>
       <c r="F5">
-        <v>3.215E-3</v>
+        <v>2.5799999999999998E-3</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2.5799999999999998E-3</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>6.43E-3</v>
+        <v>2.5799999999999998E-3</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>6.1081999999999997E-2</v>
+        <v>6.7081000000000002E-2</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -777,22 +777,22 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.2420000000000001E-3</v>
+        <v>2.6020000000000001E-3</v>
       </c>
       <c r="R5">
-        <v>3.0972E-2</v>
+        <v>2.0041E-2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.6020000000000001E-3</v>
       </c>
       <c r="T5">
-        <v>6.4850000000000003E-3</v>
+        <v>5.2040000000000003E-3</v>
       </c>
       <c r="U5">
         <v>0</v>
       </c>
       <c r="V5">
-        <v>1.2970000000000001E-2</v>
+        <v>1.0409E-2</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -801,13 +801,13 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>2.6020000000000001E-3</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>6.4850000000000003E-3</v>
+        <v>2.6020000000000001E-3</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>4.5007999999999999E-2</v>
+        <v>4.3860000000000003E-2</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.45">
@@ -827,19 +827,19 @@
         <v>0</v>
       </c>
       <c r="B6">
-        <v>5.8100000000000001E-3</v>
+        <v>2.5332E-2</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>5.8104999999999997E-2</v>
+        <v>8.6379999999999998E-2</v>
       </c>
       <c r="E6">
-        <v>1.1620999999999999E-2</v>
+        <v>9.5980000000000006E-3</v>
       </c>
       <c r="F6">
-        <v>0.66239400000000004</v>
+        <v>0.60465899999999995</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>5.8100000000000001E-3</v>
+        <v>4.7990000000000003E-3</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.15107200000000001</v>
+        <v>0.13916799999999999</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -878,19 +878,19 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>4.1022999999999997E-2</v>
+        <v>1.452E-2</v>
       </c>
       <c r="T6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>4.8399999999999997E-3</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
-        <v>1.1721000000000001E-2</v>
+        <v>1.452E-2</v>
       </c>
       <c r="X6">
         <v>0</v>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>5.8599999999999998E-3</v>
+        <v>9.6799999999999994E-3</v>
       </c>
       <c r="AA6">
         <v>0</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>4.6584E-2</v>
+        <v>8.6503999999999998E-2</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.45">
@@ -931,19 +931,19 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4.1591999999999997E-2</v>
+        <v>3.3276E-2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>3.3276E-2</v>
       </c>
       <c r="G7">
-        <v>0.37433</v>
+        <v>0.33276099999999997</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.249553</v>
+        <v>0.26620899999999997</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -976,19 +976,19 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>8.3899000000000001E-2</v>
+        <v>6.7124000000000003E-2</v>
       </c>
       <c r="U7">
         <v>0</v>
       </c>
       <c r="V7">
-        <v>4.1950000000000001E-2</v>
+        <v>6.7124000000000003E-2</v>
       </c>
       <c r="W7">
         <v>0</v>
       </c>
       <c r="X7">
-        <v>4.1950000000000001E-2</v>
+        <v>3.3562000000000002E-2</v>
       </c>
       <c r="Y7">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>0.16672600000000001</v>
+        <v>0.16666700000000001</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.45">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.33333299999999999</v>
+        <v>0.2</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="AE8">
-        <v>0.66666700000000001</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.45">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1204,22 +1204,22 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>1.1169999999999999E-2</v>
+        <v>9.1509999999999994E-3</v>
       </c>
       <c r="B10">
-        <v>0.311697</v>
+        <v>0.29202899999999998</v>
       </c>
       <c r="C10">
-        <v>5.2004000000000002E-2</v>
+        <v>5.2512999999999997E-2</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2.3159999999999999E-3</v>
       </c>
       <c r="E10">
-        <v>1.6962999999999999E-2</v>
+        <v>1.6213000000000002E-2</v>
       </c>
       <c r="F10">
-        <v>8.482E-3</v>
+        <v>1.6213000000000002E-2</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1231,13 +1231,13 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0.22334999999999999</v>
+        <v>0.22697999999999999</v>
       </c>
       <c r="K10">
-        <v>5.6540000000000002E-3</v>
+        <v>6.9480000000000002E-3</v>
       </c>
       <c r="L10">
-        <v>5.6540000000000002E-3</v>
+        <v>6.9480000000000002E-3</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -1252,13 +1252,13 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.8519999999999999E-3</v>
+        <v>8.9949999999999995E-3</v>
       </c>
       <c r="R10">
         <v>0</v>
       </c>
       <c r="S10">
-        <v>2.5663999999999999E-2</v>
+        <v>2.5696E-2</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -1279,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>5.7029999999999997E-3</v>
+        <v>9.3439999999999999E-3</v>
       </c>
       <c r="AA10">
-        <v>2.8519999999999999E-3</v>
+        <v>2.336E-3</v>
       </c>
       <c r="AB10">
         <v>0</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="AE10">
-        <v>0.327957</v>
+        <v>0.32431700000000002</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.45">
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.41636800000000002</v>
+        <v>0.30769200000000002</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1323,13 +1323,13 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>7.6923000000000005E-2</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0.166547</v>
+        <v>0.230769</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>8.3988999999999994E-2</v>
+        <v>0</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -1389,7 +1389,7 @@
         <v>0</v>
       </c>
       <c r="AE11">
-        <v>0.33309499999999997</v>
+        <v>0.38461499999999998</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.45">
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.24946399999999999</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>0.24946399999999999</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>0.251608</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -1484,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>0.24946399999999999</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.45">
@@ -1498,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1.081E-2</v>
+        <v>8.5100000000000002E-3</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1525,13 +1525,13 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0.84860899999999995</v>
+        <v>0.80842199999999997</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="O13">
-        <v>0.113508</v>
+        <v>0.14466499999999999</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1570,16 +1570,16 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>4.2909999999999997E-3</v>
       </c>
       <c r="AC13">
-        <v>5.4520000000000002E-3</v>
+        <v>8.5830000000000004E-3</v>
       </c>
       <c r="AD13">
         <v>0</v>
       </c>
       <c r="AE13">
-        <v>2.1621000000000001E-2</v>
+        <v>2.5529E-2</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.45">
@@ -1715,13 +1715,13 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0.6</v>
+        <v>0.66666700000000001</v>
       </c>
       <c r="N15">
         <v>0</v>
       </c>
       <c r="O15">
-        <v>0.4</v>
+        <v>0.33333299999999999</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1774,19 +1774,19 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>4.06E-4</v>
+        <v>3.3500000000000001E-4</v>
       </c>
       <c r="B16">
-        <v>1.01E-3</v>
+        <v>8.3500000000000002E-4</v>
       </c>
       <c r="C16">
-        <v>5.7501999999999998E-2</v>
+        <v>6.2019999999999999E-2</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>2.7720000000000002E-3</v>
+        <v>3.82E-3</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1819,25 +1819,25 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0.57417899999999999</v>
+        <v>0.53519000000000005</v>
       </c>
       <c r="Q16">
-        <v>3.5430000000000001E-3</v>
+        <v>4.3930000000000002E-3</v>
       </c>
       <c r="R16">
-        <v>0.311282</v>
+        <v>0.334673</v>
       </c>
       <c r="S16">
-        <v>6.2100000000000002E-4</v>
+        <v>2.5700000000000001E-4</v>
       </c>
       <c r="T16">
-        <v>3.418E-3</v>
+        <v>3.852E-3</v>
       </c>
       <c r="U16">
         <v>0</v>
       </c>
       <c r="V16">
-        <v>1.554E-3</v>
+        <v>1.284E-3</v>
       </c>
       <c r="W16">
         <v>0</v>
@@ -1846,16 +1846,16 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.0874999999999999E-2</v>
+        <v>1.3355000000000001E-2</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.5700000000000001E-4</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>3.1100000000000002E-4</v>
+        <v>2.5700000000000001E-4</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -1864,27 +1864,27 @@
         <v>0</v>
       </c>
       <c r="AE16">
-        <v>3.2528000000000001E-2</v>
+        <v>3.9472E-2</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>1.369E-3</v>
+        <v>1.5590000000000001E-3</v>
       </c>
       <c r="B17">
-        <v>1.1509999999999999E-3</v>
+        <v>1.8370000000000001E-3</v>
       </c>
       <c r="C17">
-        <v>5.1999999999999995E-4</v>
+        <v>7.6000000000000004E-4</v>
       </c>
       <c r="D17">
-        <v>8.4919999999999995E-3</v>
+        <v>9.8390000000000005E-3</v>
       </c>
       <c r="E17">
-        <v>2.5999999999999998E-4</v>
+        <v>2.22E-4</v>
       </c>
       <c r="F17">
-        <v>1.82E-3</v>
+        <v>2.5149999999999999E-3</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1893,19 +1893,19 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>8.7000000000000001E-5</v>
+        <v>7.3999999999999996E-5</v>
       </c>
       <c r="J17">
-        <v>2.5999999999999998E-4</v>
+        <v>2.22E-4</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>8.7000000000000001E-5</v>
+        <v>7.3999999999999996E-5</v>
       </c>
       <c r="M17">
-        <v>8.7000000000000001E-5</v>
+        <v>7.3999999999999996E-5</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -1914,28 +1914,28 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.5599999999999999E-4</v>
       </c>
       <c r="Q17">
-        <v>0.87557399999999996</v>
+        <v>0.85677000000000003</v>
       </c>
       <c r="R17">
-        <v>8.7000000000000001E-5</v>
+        <v>7.4999999999999993E-5</v>
       </c>
       <c r="S17">
-        <v>9.6925999999999998E-2</v>
+        <v>0.109162</v>
       </c>
       <c r="T17">
-        <v>2.5349999999999999E-3</v>
+        <v>2.9849999999999998E-3</v>
       </c>
       <c r="U17">
-        <v>7.8700000000000005E-4</v>
+        <v>6.7199999999999996E-4</v>
       </c>
       <c r="V17">
-        <v>1.75E-4</v>
+        <v>3.7300000000000001E-4</v>
       </c>
       <c r="W17">
-        <v>5.2400000000000005E-4</v>
+        <v>5.22E-4</v>
       </c>
       <c r="X17">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>4.6319999999999998E-3</v>
+        <v>6.1180000000000002E-3</v>
       </c>
       <c r="AA17">
         <v>0</v>
@@ -1953,13 +1953,13 @@
         <v>0</v>
       </c>
       <c r="AC17">
-        <v>8.7000000000000001E-5</v>
+        <v>7.4999999999999993E-5</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>7.4999999999999993E-5</v>
       </c>
       <c r="AE17">
-        <v>4.5409999999999999E-3</v>
+        <v>5.7400000000000003E-3</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.45">
@@ -1967,16 +1967,16 @@
         <v>0</v>
       </c>
       <c r="B18">
-        <v>1.2459999999999999E-3</v>
+        <v>1.127E-3</v>
       </c>
       <c r="C18">
-        <v>1.3501000000000001E-2</v>
+        <v>1.4147E-2</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>1.7443E-2</v>
+        <v>2.2532E-2</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1.127E-3</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2009,25 +2009,25 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2.5898999999999998E-2</v>
+        <v>2.4719000000000001E-2</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.2390000000000001E-3</v>
       </c>
       <c r="R18">
-        <v>0.838866</v>
+        <v>0.81493700000000002</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="T18">
-        <v>1.2570000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="U18">
         <v>0</v>
       </c>
       <c r="V18">
-        <v>1.2570000000000001E-3</v>
+        <v>3.4090000000000001E-3</v>
       </c>
       <c r="W18">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="Y18">
-        <v>4.3982E-2</v>
+        <v>5.2268000000000002E-2</v>
       </c>
       <c r="Z18">
-        <v>1.2570000000000001E-3</v>
+        <v>1.1360000000000001E-3</v>
       </c>
       <c r="AA18">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="AE18">
-        <v>5.5292000000000001E-2</v>
+        <v>6.1358999999999997E-2</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.45">
@@ -2062,19 +2062,19 @@
         <v>0</v>
       </c>
       <c r="B19">
-        <v>7.0939999999999996E-3</v>
+        <v>9.1249999999999994E-3</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>1.2428E-2</v>
+        <v>1.3365999999999999E-2</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>1.6948000000000001E-2</v>
+        <v>3.1505999999999999E-2</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2086,16 +2086,16 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>2.2599999999999999E-3</v>
+        <v>2.8639999999999998E-3</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>3.3899999999999998E-3</v>
+        <v>4.7739999999999996E-3</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>9.5500000000000001E-4</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -2107,25 +2107,25 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>0.16041900000000001</v>
+        <v>0.114273</v>
       </c>
       <c r="R19">
-        <v>3.2490000000000002E-3</v>
+        <v>2.745E-3</v>
       </c>
       <c r="S19">
-        <v>0.63586600000000004</v>
+        <v>0.64132400000000001</v>
       </c>
       <c r="T19">
-        <v>5.6979999999999999E-3</v>
+        <v>7.7039999999999999E-3</v>
       </c>
       <c r="U19">
-        <v>1.14E-3</v>
+        <v>9.6299999999999999E-4</v>
       </c>
       <c r="V19">
-        <v>5.6979999999999999E-3</v>
+        <v>6.7409999999999996E-3</v>
       </c>
       <c r="W19">
-        <v>1.14E-3</v>
+        <v>2.8890000000000001E-3</v>
       </c>
       <c r="X19">
         <v>0</v>
@@ -2134,13 +2134,13 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>9.2302999999999996E-2</v>
+        <v>9.9183999999999994E-2</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>9.6299999999999999E-4</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="AE19">
-        <v>5.237E-2</v>
+        <v>6.0624999999999998E-2</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.45">
@@ -2160,31 +2160,31 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>2.5392000000000001E-2</v>
+        <v>2.2685E-2</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>4.0439999999999999E-3</v>
+        <v>1.2467000000000001E-2</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>1.2132E-2</v>
+        <v>9.3500000000000007E-3</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>8.0879999999999997E-3</v>
+        <v>9.3500000000000007E-3</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>4.0439999999999999E-3</v>
+        <v>3.117E-3</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.143E-3</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -2211,16 +2211,16 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>0.73419699999999999</v>
+        <v>0.70413000000000003</v>
       </c>
       <c r="U20">
         <v>0</v>
       </c>
       <c r="V20">
-        <v>0.19170699999999999</v>
+        <v>0.20746700000000001</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>3.143E-3</v>
       </c>
       <c r="X20">
         <v>0</v>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>1.6315E-2</v>
+        <v>1.2574E-2</v>
       </c>
       <c r="AB20">
         <v>0</v>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="AE20">
-        <v>4.0790000000000002E-3</v>
+        <v>1.2574E-2</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.45">
@@ -2258,19 +2258,19 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>2.6162999999999999E-2</v>
+        <v>2.0076E-2</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>3.9245000000000002E-2</v>
+        <v>4.0150999999999999E-2</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>1.3082E-2</v>
+        <v>1.0038E-2</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2297,25 +2297,25 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.7613000000000001E-2</v>
+        <v>2.8861000000000001E-2</v>
       </c>
       <c r="R21">
         <v>0</v>
       </c>
       <c r="S21">
-        <v>1.3194000000000001E-2</v>
+        <v>2.0247999999999999E-2</v>
       </c>
       <c r="T21">
-        <v>1.3194000000000001E-2</v>
+        <v>1.0123999999999999E-2</v>
       </c>
       <c r="U21">
-        <v>0.35624299999999998</v>
+        <v>0.334096</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.422213</v>
+        <v>0.43533699999999997</v>
       </c>
       <c r="X21">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="AE21">
-        <v>7.9052999999999998E-2</v>
+        <v>0.10106900000000001</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.45">
@@ -2368,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>6.2E-2</v>
+        <v>9.9232000000000001E-2</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2401,13 +2401,13 @@
         <v>0</v>
       </c>
       <c r="T22">
-        <v>0.18759999999999999</v>
+        <v>0.10008499999999999</v>
       </c>
       <c r="U22">
         <v>0</v>
       </c>
       <c r="V22">
-        <v>0.43773299999999998</v>
+        <v>0.60051200000000005</v>
       </c>
       <c r="W22">
         <v>0</v>
@@ -2422,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>0.25013299999999999</v>
+        <v>0.15012800000000001</v>
       </c>
       <c r="AB22">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>6.2533000000000005E-2</v>
+        <v>5.0042999999999997E-2</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.45">
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0.19863400000000001</v>
+        <v>0.16548099999999999</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.20034099999999999</v>
+        <v>0.33380700000000002</v>
       </c>
       <c r="X23">
         <v>0</v>
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>0.601024</v>
+        <v>0.50071100000000002</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.45">
@@ -2635,13 +2635,13 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>3.0896E-2</v>
+        <v>3.6394999999999997E-2</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>9.2688999999999994E-2</v>
+        <v>0.10918600000000001</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2674,13 +2674,13 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.7840000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
       </c>
       <c r="R25">
-        <v>0.29766100000000001</v>
+        <v>0.24873600000000001</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="Y25">
-        <v>0.24929499999999999</v>
+        <v>0.29366500000000001</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>0.31161899999999998</v>
+        <v>0.31201899999999999</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.45">
@@ -2739,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0.106327</v>
+        <v>3.2001000000000002E-2</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>3.2001000000000002E-2</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -2772,13 +2772,13 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>7.1494000000000002E-2</v>
+        <v>6.4551999999999998E-2</v>
       </c>
       <c r="R26">
         <v>0</v>
       </c>
       <c r="S26">
-        <v>0.28597499999999998</v>
+        <v>0.32275799999999999</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -2787,10 +2787,10 @@
         <v>0</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>3.2275999999999999E-2</v>
       </c>
       <c r="W26">
-        <v>3.5747000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="X26">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="Z26">
-        <v>0.25022800000000001</v>
+        <v>0.25820599999999999</v>
       </c>
       <c r="AA26">
         <v>0</v>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>0.25022800000000001</v>
+        <v>0.25820599999999999</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.45">
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>5.2229999999999999E-2</v>
+        <v>3.9685999999999999E-2</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="V28">
-        <v>5.2678999999999997E-2</v>
+        <v>4.0027E-2</v>
       </c>
       <c r="W28">
         <v>0</v>
@@ -2995,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.79018200000000005</v>
+        <v>0.84057300000000001</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="AE28">
-        <v>0.104909</v>
+        <v>7.9713000000000006E-2</v>
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.45">
@@ -3093,13 +3093,13 @@
         <v>0</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>0.50214000000000003</v>
       </c>
       <c r="AD29">
         <v>0</v>
       </c>
       <c r="AE29">
-        <v>1</v>
+        <v>0.49786000000000002</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.45">

--- a/Belle2/data.xlsx
+++ b/Belle2/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\purol\OneDrive\바탕 화면\github\Belle2_script\Belle2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwpark\Desktop\git\Belle2_script\Belle2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6B750F-40BC-4D9D-98AA-572A35688932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0BBDE9-F265-428B-B99D-22BABF7A5E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,19 +38,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.000000000_ "/>
+    <numFmt numFmtId="164" formatCode="0.000000000_ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -78,7 +78,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -360,80 +360,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE30"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="31" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="31" width="12.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31">
       <c r="A1" s="1">
-        <v>4.4878373309921327E-3</v>
+        <v>0.70319299999999996</v>
       </c>
       <c r="B1" s="1">
-        <v>1.0322286952283777E-3</v>
+        <v>0.20138800000000001</v>
       </c>
       <c r="C1" s="1">
-        <v>3.0464792904768097E-5</v>
+        <v>1.0593E-2</v>
       </c>
       <c r="D1" s="1">
-        <v>2.6716344706975559E-5</v>
+        <v>4.2209999999999999E-3</v>
       </c>
       <c r="E1" s="1">
-        <v>5.0348603910442167E-6</v>
+        <v>1.913E-3</v>
       </c>
       <c r="F1" s="1">
-        <v>1.4630440280828113E-5</v>
+        <v>3.2269999999999998E-3</v>
       </c>
       <c r="G1" s="1">
-        <v>0</v>
+        <v>6.0999999999999999E-5</v>
       </c>
       <c r="H1" s="1">
         <v>0</v>
       </c>
       <c r="I1" s="1">
-        <v>2.3395614046516239E-6</v>
+        <v>0</v>
       </c>
       <c r="J1" s="1">
-        <v>2.4968956289863822E-4</v>
+        <v>6.8139999999999997E-3</v>
       </c>
       <c r="K1" s="1">
-        <v>3.3674072783069648E-6</v>
+        <v>6.8999999999999997E-5</v>
       </c>
       <c r="L1" s="1">
-        <v>0</v>
+        <v>3.2899999999999997E-4</v>
       </c>
       <c r="M1" s="1">
-        <v>2.5255842521024153E-5</v>
+        <v>1.3999999999999999E-4</v>
       </c>
       <c r="N1" s="1">
-        <v>0</v>
+        <v>2.0999999999999999E-5</v>
       </c>
       <c r="O1" s="1">
         <v>0</v>
       </c>
       <c r="P1" s="1">
-        <v>0</v>
+        <v>7.6000000000000004E-5</v>
       </c>
       <c r="Q1" s="1">
-        <v>8.4956923683622039E-5</v>
+        <v>3.6422000000000003E-2</v>
       </c>
       <c r="R1" s="1">
-        <v>0</v>
+        <v>1.9799999999999999E-4</v>
       </c>
       <c r="S1" s="1">
-        <v>1.7668874358662493E-5</v>
+        <v>6.3990000000000002E-3</v>
       </c>
       <c r="T1" s="1">
-        <v>1.0133897987694987E-6</v>
+        <v>1.9599999999999999E-4</v>
       </c>
       <c r="U1" s="1">
-        <v>0</v>
+        <v>2.9700000000000001E-4</v>
       </c>
       <c r="V1" s="1">
-        <v>0</v>
+        <v>1.3100000000000001E-4</v>
       </c>
       <c r="W1" s="1">
-        <v>0</v>
+        <v>2.0999999999999999E-5</v>
       </c>
       <c r="X1" s="1">
         <v>0</v>
@@ -442,93 +442,93 @@
         <v>0</v>
       </c>
       <c r="Z1" s="1">
-        <v>6.5784432455163958E-6</v>
+        <v>3.39E-4</v>
       </c>
       <c r="AA1" s="1">
         <v>0</v>
       </c>
       <c r="AB1" s="1">
-        <v>0</v>
+        <v>7.6000000000000004E-5</v>
       </c>
       <c r="AC1" s="1">
         <v>0</v>
       </c>
       <c r="AD1" s="1">
-        <v>0</v>
+        <v>1.4E-5</v>
       </c>
       <c r="AE1" s="1">
-        <v>5.966120936099942E-5</v>
+        <v>2.3859999999999999E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31">
       <c r="A2" s="1">
-        <v>2.1756051548522972E-4</v>
+        <v>9.1799000000000006E-2</v>
       </c>
       <c r="B2" s="1">
-        <v>1.7402543931139916E-3</v>
+        <v>0.70426500000000003</v>
       </c>
       <c r="C2" s="1">
-        <v>1.2028295535579682E-5</v>
+        <v>1.1421000000000001E-2</v>
       </c>
       <c r="D2" s="1">
-        <v>1.1302702548573267E-5</v>
+        <v>3.7959999999999999E-3</v>
       </c>
       <c r="E2" s="1">
-        <v>1.3425553574177052E-5</v>
+        <v>7.7349999999999997E-3</v>
       </c>
       <c r="F2" s="1">
-        <v>8.7790391885090952E-6</v>
+        <v>1.0496E-2</v>
       </c>
       <c r="G2" s="1">
-        <v>2.9117787876360697E-6</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0</v>
+        <v>6.8999999999999997E-5</v>
       </c>
       <c r="J2" s="1">
-        <v>1.1968724283290461E-3</v>
+        <v>6.4408000000000007E-2</v>
       </c>
       <c r="K2" s="1">
-        <v>1.0093313350057647E-5</v>
+        <v>2.7999999999999998E-4</v>
       </c>
       <c r="L2" s="1">
-        <v>7.5388982937615898E-6</v>
+        <v>1.0300000000000001E-3</v>
       </c>
       <c r="M2" s="1">
-        <v>6.3223234920179669E-6</v>
+        <v>3.2200000000000002E-4</v>
       </c>
       <c r="N2" s="1">
-        <v>1.6000430064469459E-5</v>
+        <v>1.3899999999999999E-4</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
       </c>
       <c r="P2" s="1">
-        <v>3.4826001750567325E-7</v>
+        <v>1.03E-4</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.7474672368046533E-5</v>
+        <v>1.8183999999999999E-2</v>
       </c>
       <c r="R2" s="1">
-        <v>9.1854537678022612E-7</v>
+        <v>2.12E-4</v>
       </c>
       <c r="S2" s="1">
-        <v>4.7253941032535393E-5</v>
+        <v>3.0817000000000001E-2</v>
       </c>
       <c r="T2" s="1">
-        <v>0</v>
+        <v>4.26E-4</v>
       </c>
       <c r="U2" s="1">
         <v>0</v>
       </c>
       <c r="V2" s="1">
-        <v>1.4426643482414495E-6</v>
+        <v>1.4100000000000001E-4</v>
       </c>
       <c r="W2" s="1">
-        <v>0</v>
+        <v>6.9999999999999994E-5</v>
       </c>
       <c r="X2" s="1">
         <v>0</v>
@@ -537,57 +537,57 @@
         <v>0</v>
       </c>
       <c r="Z2" s="1">
-        <v>1.9735329736549185E-5</v>
+        <v>2.2599999999999999E-3</v>
       </c>
       <c r="AA2" s="1">
-        <v>0</v>
+        <v>3.68E-4</v>
       </c>
       <c r="AB2" s="1">
-        <v>0</v>
+        <v>5.5999999999999999E-5</v>
       </c>
       <c r="AC2" s="1">
         <v>0</v>
       </c>
       <c r="AD2" s="1">
-        <v>3.146456303588084E-5</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="1">
-        <v>8.1920896871578172E-5</v>
+        <v>5.1602000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31">
       <c r="A3" s="1">
-        <v>0</v>
+        <v>7.3300000000000004E-4</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
       </c>
       <c r="C3" s="1">
-        <v>3.9845578980696053E-4</v>
+        <v>0.81957199999999997</v>
       </c>
       <c r="D3" s="1">
-        <v>1.5417724521470638E-6</v>
+        <v>1.4239999999999999E-3</v>
       </c>
       <c r="E3" s="1">
-        <v>1.0824338679143857E-4</v>
+        <v>0.128917</v>
       </c>
       <c r="F3" s="1">
-        <v>7.3239391155516181E-7</v>
+        <v>6.6799999999999997E-4</v>
       </c>
       <c r="G3" s="1">
-        <v>5.81585445678633E-6</v>
+        <v>2.6220000000000002E-3</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>0</v>
+        <v>4.9299999999999995E-4</v>
       </c>
       <c r="J3" s="1">
-        <v>2.7171422954768897E-6</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>6.7259060717506837E-6</v>
+        <v>8.1930000000000006E-3</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -602,25 +602,25 @@
         <v>0</v>
       </c>
       <c r="P3" s="1">
-        <v>3.5246413517213653E-6</v>
+        <v>3.6679999999999998E-3</v>
       </c>
       <c r="Q3" s="1">
-        <v>7.8471072742595723E-7</v>
+        <v>2.5790000000000001E-3</v>
       </c>
       <c r="R3" s="1">
-        <v>2.0549435056253493E-6</v>
+        <v>1.913E-3</v>
       </c>
       <c r="S3" s="1">
-        <v>4.1082822830623254E-7</v>
+        <v>0</v>
       </c>
       <c r="T3" s="1">
-        <v>1.1149968711858057E-5</v>
+        <v>1.6268999999999999E-2</v>
       </c>
       <c r="U3" s="1">
-        <v>0</v>
+        <v>4.9799999999999996E-4</v>
       </c>
       <c r="V3" s="1">
-        <v>0</v>
+        <v>4.8269999999999997E-3</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
@@ -629,16 +629,16 @@
         <v>0</v>
       </c>
       <c r="Y3" s="1">
-        <v>0</v>
+        <v>3.1700000000000001E-4</v>
       </c>
       <c r="Z3" s="1">
         <v>0</v>
       </c>
       <c r="AA3" s="1">
-        <v>0</v>
+        <v>8.0199999999999998E-4</v>
       </c>
       <c r="AB3" s="1">
-        <v>0</v>
+        <v>1.16E-4</v>
       </c>
       <c r="AC3" s="1">
         <v>0</v>
@@ -647,78 +647,78 @@
         <v>0</v>
       </c>
       <c r="AE3" s="1">
-        <v>2.1795342821200747E-6</v>
+        <v>6.3889999999999997E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31">
       <c r="A4" s="1">
-        <v>0</v>
+        <v>3.4299999999999999E-4</v>
       </c>
       <c r="B4" s="1">
-        <v>7.0347109225527622E-7</v>
+        <v>1.9380000000000001E-3</v>
       </c>
       <c r="C4" s="1">
-        <v>2.0064778455379013E-6</v>
+        <v>4.1920000000000004E-3</v>
       </c>
       <c r="D4" s="1">
-        <v>7.8094789024932667E-4</v>
+        <v>0.61865899999999996</v>
       </c>
       <c r="E4" s="1">
-        <v>4.2003470046672123E-7</v>
+        <v>2.5500000000000002E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>2.4945762888575534E-4</v>
+        <v>0.26722000000000001</v>
       </c>
       <c r="G4" s="1">
-        <v>2.9117787876360697E-6</v>
+        <v>2.7039999999999998E-3</v>
       </c>
       <c r="H4" s="1">
-        <v>4.223951917484036E-5</v>
+        <v>1.214E-3</v>
       </c>
       <c r="I4" s="1">
-        <v>4.6729334934179252E-6</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>2.7171422954768897E-6</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
         <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>5.6546729851088579E-5</v>
+        <v>1.8742000000000002E-2</v>
       </c>
       <c r="M4" s="1">
-        <v>1.2627921260512077E-5</v>
+        <v>0</v>
       </c>
       <c r="N4" s="1">
-        <v>1.6000430064469459E-5</v>
+        <v>0</v>
       </c>
       <c r="O4" s="1">
         <v>0</v>
       </c>
       <c r="P4" s="1">
-        <v>6.9992877906523568E-7</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="1">
-        <v>4.0315123760658122E-6</v>
+        <v>2.3116999999999999E-2</v>
       </c>
       <c r="R4" s="1">
         <v>0</v>
       </c>
       <c r="S4" s="1">
-        <v>2.8768844453084591E-6</v>
+        <v>9.3550000000000005E-3</v>
       </c>
       <c r="T4" s="1">
-        <v>5.0669489938474934E-7</v>
+        <v>1.0870000000000001E-3</v>
       </c>
       <c r="U4" s="1">
-        <v>4.5591317694674751E-5</v>
+        <v>1.8540999999999998E-2</v>
       </c>
       <c r="V4" s="1">
-        <v>0</v>
+        <v>9.4799999999999995E-4</v>
       </c>
       <c r="W4" s="1">
-        <v>2.2916916549976316E-6</v>
+        <v>4.5890000000000002E-3</v>
       </c>
       <c r="X4" s="1">
         <v>0</v>
@@ -727,13 +727,13 @@
         <v>0</v>
       </c>
       <c r="Z4" s="1">
-        <v>0</v>
+        <v>8.8900000000000003E-4</v>
       </c>
       <c r="AA4" s="1">
         <v>0</v>
       </c>
       <c r="AB4" s="1">
-        <v>6.2556824517614903E-6</v>
+        <v>2.5999999999999998E-4</v>
       </c>
       <c r="AC4" s="1">
         <v>0</v>
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="AE4" s="1">
-        <v>8.122096939628975E-6</v>
+        <v>2.5947000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31">
       <c r="A5" s="1">
         <v>0</v>
       </c>
@@ -753,34 +753,34 @@
         <v>0</v>
       </c>
       <c r="C5" s="1">
-        <v>1.9613638086262417E-5</v>
+        <v>0.15640200000000001</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>1.6639999999999999E-3</v>
       </c>
       <c r="E5" s="1">
-        <v>1.5649181719954713E-4</v>
+        <v>0.69167199999999995</v>
       </c>
       <c r="F5" s="1">
-        <v>2.9257005461595089E-6</v>
+        <v>1.9710000000000001E-3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>6.7629999999999999E-3</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>7.0124948980695483E-6</v>
+        <v>4.0769999999999999E-3</v>
       </c>
       <c r="J5" s="1">
-        <v>2.7171422954768897E-6</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>1.1099972139604439E-4</v>
+        <v>5.4349000000000001E-2</v>
       </c>
       <c r="L5" s="1">
-        <v>0</v>
+        <v>1.4599999999999999E-3</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
@@ -792,40 +792,40 @@
         <v>0</v>
       </c>
       <c r="P5" s="1">
-        <v>3.4826001750567325E-7</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="1">
-        <v>0</v>
+        <v>2.101E-3</v>
       </c>
       <c r="R5" s="1">
-        <v>0</v>
+        <v>7.5560000000000002E-3</v>
       </c>
       <c r="S5" s="1">
-        <v>0</v>
+        <v>8.5300000000000003E-4</v>
       </c>
       <c r="T5" s="1">
-        <v>2.0267795975389974E-6</v>
+        <v>1.0884E-2</v>
       </c>
       <c r="U5" s="1">
         <v>0</v>
       </c>
       <c r="V5" s="1">
-        <v>4.3279930447243483E-6</v>
+        <v>2.6445E-2</v>
       </c>
       <c r="W5" s="1">
-        <v>2.2916916549976316E-6</v>
+        <v>0</v>
       </c>
       <c r="X5" s="1">
         <v>0</v>
       </c>
       <c r="Y5" s="1">
-        <v>2.6569655652412727E-6</v>
+        <v>1.572E-3</v>
       </c>
       <c r="Z5" s="1">
         <v>0</v>
       </c>
       <c r="AA5" s="1">
-        <v>0</v>
+        <v>6.4650000000000003E-3</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
@@ -837,36 +837,36 @@
         <v>0</v>
       </c>
       <c r="AE5" s="1">
-        <v>2.7734757379120645E-6</v>
+        <v>2.5767000000000002E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31">
       <c r="A6" s="1">
         <v>0</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>5.04E-4</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
+        <v>4.5399999999999998E-4</v>
       </c>
       <c r="D6" s="1">
-        <v>2.928551186465751E-5</v>
+        <v>0.105518</v>
       </c>
       <c r="E6" s="1">
-        <v>4.2003470046672123E-7</v>
+        <v>5.6509999999999998E-3</v>
       </c>
       <c r="F6" s="1">
-        <v>1.7995964683926833E-4</v>
+        <v>0.65035200000000004</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>2.8147252406888329E-5</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>2.3395614046516239E-6</v>
+        <v>2.274E-3</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -875,10 +875,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>1.0179010490941144E-4</v>
+        <v>0.12246700000000001</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
+        <v>1.4090000000000001E-3</v>
       </c>
       <c r="N6" s="1">
         <v>0</v>
@@ -890,25 +890,25 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1">
-        <v>7.008704301671282E-7</v>
+        <v>3.7200000000000002E-3</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>2.4649693698373953E-6</v>
+        <v>1.7812000000000001E-2</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>2.8489862933686655E-6</v>
+        <v>7.9039999999999996E-3</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>1.3750149929985789E-5</v>
+        <v>9.8899999999999995E-3</v>
       </c>
       <c r="X6" s="1">
         <v>0</v>
@@ -917,10 +917,10 @@
         <v>0</v>
       </c>
       <c r="Z6" s="1">
-        <v>3.2892216227581979E-6</v>
+        <v>4.4990000000000004E-3</v>
       </c>
       <c r="AA6" s="1">
-        <v>0</v>
+        <v>2.4359999999999998E-3</v>
       </c>
       <c r="AB6" s="1">
         <v>0</v>
@@ -932,10 +932,10 @@
         <v>0</v>
       </c>
       <c r="AE6" s="1">
-        <v>3.7640777419184922E-6</v>
+        <v>6.5107999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31">
       <c r="A7" s="1">
         <v>0</v>
       </c>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="1">
-        <v>0</v>
+        <v>1.7874000000000001E-2</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>6.6893880930771511E-5</v>
+        <v>0.59576399999999996</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>9.3458669868358505E-6</v>
+        <v>0.172628</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="V7" s="1">
-        <v>0</v>
+        <v>0.12711900000000001</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
       </c>
       <c r="X7" s="1">
-        <v>0</v>
+        <v>1.4912E-2</v>
       </c>
       <c r="Y7" s="1">
         <v>0</v>
@@ -1027,10 +1027,10 @@
         <v>0</v>
       </c>
       <c r="AE7" s="1">
-        <v>1.9833027410721914E-7</v>
+        <v>7.1703000000000003E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31">
       <c r="A8" s="1">
         <v>0</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>2.8147252406888329E-5</v>
+        <v>0.50224800000000003</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="1">
-        <v>2.2916916549976316E-6</v>
+        <v>0</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
@@ -1122,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="AE8" s="1">
-        <v>7.9227172989920876E-7</v>
+        <v>0.49775200000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:31">
       <c r="A9" s="1">
         <v>0</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>1.1685428391487474E-5</v>
+        <v>0.79491599999999996</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -1217,27 +1217,27 @@
         <v>0</v>
       </c>
       <c r="AE9" s="1">
-        <v>3.9666054821443828E-7</v>
+        <v>0.20508399999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:31">
       <c r="A10" s="1">
-        <v>3.7040671781540215E-6</v>
+        <v>2.274E-2</v>
       </c>
       <c r="B10" s="1">
-        <v>5.3543550860447947E-5</v>
+        <v>0.26078600000000002</v>
       </c>
       <c r="C10" s="1">
-        <v>1.302677726640716E-6</v>
+        <v>1.5987000000000001E-2</v>
       </c>
       <c r="D10" s="1">
-        <v>2.5691671576819565E-6</v>
+        <v>4.6569999999999997E-3</v>
       </c>
       <c r="E10" s="1">
-        <v>2.5168745940664645E-6</v>
+        <v>3.4019000000000001E-2</v>
       </c>
       <c r="F10" s="1">
-        <v>8.0466452769539324E-6</v>
+        <v>2.3206999999999998E-2</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1249,19 +1249,19 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>5.2108751133256791E-4</v>
+        <v>0.30868800000000002</v>
       </c>
       <c r="K10" s="1">
-        <v>3.3674072783069648E-6</v>
+        <v>3.5370000000000002E-3</v>
       </c>
       <c r="L10" s="1">
-        <v>3.7744417947574584E-6</v>
+        <v>9.2820000000000003E-3</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>0</v>
+        <v>7.0200000000000004E-4</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1">
-        <v>5.6764475233118088E-7</v>
+        <v>1.3656E-2</v>
       </c>
       <c r="R10" s="1">
-        <v>0</v>
+        <v>1.186E-3</v>
       </c>
       <c r="S10" s="1">
-        <v>7.80682318498325E-6</v>
+        <v>2.9184000000000002E-2</v>
       </c>
       <c r="T10" s="1">
         <v>0</v>
@@ -1285,19 +1285,19 @@
         <v>0</v>
       </c>
       <c r="V10" s="1">
-        <v>0</v>
+        <v>1.3079999999999999E-3</v>
       </c>
       <c r="W10" s="1">
-        <v>0</v>
+        <v>7.4299999999999995E-4</v>
       </c>
       <c r="X10" s="1">
         <v>0</v>
       </c>
       <c r="Y10" s="1">
-        <v>0</v>
+        <v>1.9369999999999999E-3</v>
       </c>
       <c r="Z10" s="1">
-        <v>2.9611696249328429E-5</v>
+        <v>1.3997000000000001E-2</v>
       </c>
       <c r="AA10" s="1">
         <v>0</v>
@@ -1309,13 +1309,13 @@
         <v>0</v>
       </c>
       <c r="AD10" s="1">
-        <v>3.146456303588084E-5</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="1">
-        <v>3.3281708854944776E-5</v>
+        <v>0.25438499999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:31">
       <c r="A11" s="1">
         <v>0</v>
       </c>
@@ -1323,16 +1323,16 @@
         <v>0</v>
       </c>
       <c r="C11" s="1">
-        <v>9.9901030770986136E-8</v>
+        <v>5.9242000000000003E-2</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>2.5168745940664645E-6</v>
+        <v>0.37784400000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>3.6239E-2</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>1.6819219421808332E-5</v>
+        <v>0.30583100000000002</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
@@ -1362,13 +1362,13 @@
         <v>0</v>
       </c>
       <c r="P11" s="1">
-        <v>0</v>
+        <v>2.3789000000000001E-2</v>
       </c>
       <c r="Q11" s="1">
         <v>0</v>
       </c>
       <c r="R11" s="1">
-        <v>2.172779426926943E-7</v>
+        <v>0</v>
       </c>
       <c r="S11" s="1">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="1">
-        <v>0</v>
+        <v>3.6655E-2</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
@@ -1392,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="Z11" s="1">
-        <v>3.2892216227581979E-6</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="1">
-        <v>0</v>
+        <v>2.9106E-2</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
@@ -1407,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="AE11" s="1">
-        <v>7.9279641316404261E-7</v>
+        <v>0.131295</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:31">
       <c r="A12" s="1">
         <v>0</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>2.1952441846349159E-6</v>
+        <v>0.51047600000000004</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>2.3395614046516239E-6</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>1.507779658752318E-5</v>
+        <v>0.20813999999999999</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>0</v>
       </c>
       <c r="U12" s="1">
-        <v>0</v>
+        <v>1.2876E-2</v>
       </c>
       <c r="V12" s="1">
         <v>0</v>
       </c>
       <c r="W12" s="1">
-        <v>2.2916916549976316E-6</v>
+        <v>0</v>
       </c>
       <c r="X12" s="1">
         <v>0</v>
@@ -1502,27 +1502,27 @@
         <v>0</v>
       </c>
       <c r="AE12" s="1">
-        <v>3.9613586494960438E-7</v>
+        <v>0.268507</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:31">
       <c r="A13" s="1">
         <v>0</v>
       </c>
       <c r="B13" s="1">
-        <v>0</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="C13" s="1">
         <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>5.1437774661217142E-7</v>
+        <v>2.0486000000000001E-2</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>1.4628502730797544E-6</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1543,13 +1543,13 @@
         <v>0</v>
       </c>
       <c r="M13" s="1">
-        <v>7.8937052170843368E-4</v>
+        <v>0.83040700000000001</v>
       </c>
       <c r="N13" s="1">
         <v>0</v>
       </c>
       <c r="O13" s="1">
-        <v>3.4567005597557646E-4</v>
+        <v>0.10624599999999999</v>
       </c>
       <c r="P13" s="1">
         <v>0</v>
@@ -1591,16 +1591,16 @@
         <v>0</v>
       </c>
       <c r="AC13" s="1">
-        <v>7.1014116654526216E-5</v>
+        <v>7.4469999999999996E-3</v>
       </c>
       <c r="AD13" s="1">
         <v>0</v>
       </c>
       <c r="AE13" s="1">
-        <v>0</v>
+        <v>3.3314999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:31">
       <c r="A14" s="1">
         <v>0</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>1.6000430064469459E-5</v>
+        <v>1</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -1695,7 +1695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:31">
       <c r="A15" s="1">
         <v>0</v>
       </c>
@@ -1733,13 +1733,13 @@
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>3.1578166013042114E-5</v>
+        <v>0.41548499999999999</v>
       </c>
       <c r="N15" s="1">
         <v>0</v>
       </c>
       <c r="O15" s="1">
-        <v>2.1998698722452414E-4</v>
+        <v>0.24929100000000001</v>
       </c>
       <c r="P15" s="1">
         <v>0</v>
@@ -1781,30 +1781,30 @@
         <v>0</v>
       </c>
       <c r="AC15" s="1">
-        <v>0</v>
+        <v>8.4053000000000003E-2</v>
       </c>
       <c r="AD15" s="1">
         <v>0</v>
       </c>
       <c r="AE15" s="1">
-        <v>0</v>
+        <v>0.25117200000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:31">
       <c r="A16" s="1">
-        <v>0</v>
+        <v>2.9700000000000001E-4</v>
       </c>
       <c r="B16" s="1">
-        <v>0</v>
+        <v>5.7200000000000003E-4</v>
       </c>
       <c r="C16" s="1">
-        <v>1.4913003871202205E-5</v>
+        <v>8.4012000000000003E-2</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>2.7099999999999997E-4</v>
       </c>
       <c r="E16" s="1">
-        <v>8.389581980221548E-7</v>
+        <v>9.1739999999999999E-3</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1816,13 +1816,13 @@
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>0</v>
+        <v>1.6699999999999999E-4</v>
       </c>
       <c r="J16" s="1">
         <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>5.0699999999999996E-4</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>
@@ -1831,31 +1831,31 @@
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <v>0</v>
+        <v>2.1499999999999999E-4</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
       </c>
       <c r="P16" s="1">
-        <v>4.7791500633940034E-4</v>
+        <v>0.72145000000000004</v>
       </c>
       <c r="Q16" s="1">
-        <v>1.3767610457400162E-6</v>
+        <v>2.3040000000000001E-3</v>
       </c>
       <c r="R16" s="1">
-        <v>9.5960975833040102E-5</v>
+        <v>0.150728</v>
       </c>
       <c r="S16" s="1">
-        <v>0</v>
+        <v>2.05E-4</v>
       </c>
       <c r="T16" s="1">
-        <v>2.0267795975389974E-6</v>
+        <v>4.9290000000000002E-3</v>
       </c>
       <c r="U16" s="1">
         <v>0</v>
       </c>
       <c r="V16" s="1">
-        <v>1.4426643482414495E-6</v>
+        <v>2.2409999999999999E-3</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
@@ -1864,16 +1864,16 @@
         <v>0</v>
       </c>
       <c r="Y16" s="1">
-        <v>1.8605787966120764E-5</v>
+        <v>4.5869999999999999E-3</v>
       </c>
       <c r="Z16" s="1">
-        <v>0</v>
+        <v>3.7199999999999999E-4</v>
       </c>
       <c r="AA16" s="1">
         <v>0</v>
       </c>
       <c r="AB16" s="1">
-        <v>0</v>
+        <v>1.36E-4</v>
       </c>
       <c r="AC16" s="1">
         <v>0</v>
@@ -1882,30 +1882,30 @@
         <v>0</v>
       </c>
       <c r="AE16" s="1">
-        <v>6.5915958561084498E-6</v>
+        <v>1.7833000000000002E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:31">
       <c r="A17" s="1">
-        <v>5.4068918741769458E-6</v>
+        <v>3.4099999999999998E-3</v>
       </c>
       <c r="B17" s="1">
-        <v>4.9126787538728072E-6</v>
+        <v>3.7309999999999999E-3</v>
       </c>
       <c r="C17" s="1">
-        <v>1.9953777310077918E-7</v>
+        <v>1.7110000000000001E-3</v>
       </c>
       <c r="D17" s="1">
-        <v>4.5726548728594697E-5</v>
+        <v>2.4098000000000001E-2</v>
       </c>
       <c r="E17" s="1">
-        <v>0</v>
+        <v>3.9399999999999998E-4</v>
       </c>
       <c r="F17" s="1">
-        <v>1.2437133646223767E-5</v>
+        <v>1.2599000000000001E-2</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>8.1099999999999998E-4</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -1914,16 +1914,16 @@
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>0</v>
+        <v>3.4099999999999999E-4</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>3.7744417947574584E-6</v>
+        <v>6.1899999999999998E-4</v>
       </c>
       <c r="M17" s="1">
-        <v>0</v>
+        <v>1.4799999999999999E-4</v>
       </c>
       <c r="N17" s="1">
         <v>0</v>
@@ -1932,28 +1932,28 @@
         <v>0</v>
       </c>
       <c r="P17" s="1">
-        <v>1.7634569238786455E-6</v>
+        <v>1.751E-3</v>
       </c>
       <c r="Q17" s="1">
-        <v>1.0700112195171929E-3</v>
+        <v>0.77739800000000003</v>
       </c>
       <c r="R17" s="1">
-        <v>0</v>
+        <v>2.1100000000000001E-4</v>
       </c>
       <c r="S17" s="1">
-        <v>3.3817575587875441E-4</v>
+        <v>0.14973</v>
       </c>
       <c r="T17" s="1">
-        <v>1.419013810816655E-5</v>
+        <v>4.4130000000000003E-3</v>
       </c>
       <c r="U17" s="1">
-        <v>5.6979725867373309E-6</v>
+        <v>1.9919999999999998E-3</v>
       </c>
       <c r="V17" s="1">
-        <v>2.1639965223621742E-6</v>
+        <v>9.4499999999999998E-4</v>
       </c>
       <c r="W17" s="1">
-        <v>2.2916916549976316E-6</v>
+        <v>4.3199999999999998E-4</v>
       </c>
       <c r="X17" s="1">
         <v>0</v>
@@ -1962,42 +1962,42 @@
         <v>0</v>
       </c>
       <c r="Z17" s="1">
-        <v>8.2247943857964239E-5</v>
+        <v>7.5319999999999996E-3</v>
       </c>
       <c r="AA17" s="1">
-        <v>0</v>
+        <v>1.36E-4</v>
       </c>
       <c r="AB17" s="1">
-        <v>0</v>
+        <v>3.8499999999999998E-4</v>
       </c>
       <c r="AC17" s="1">
-        <v>0</v>
+        <v>1.6000000000000001E-4</v>
       </c>
       <c r="AD17" s="1">
-        <v>0</v>
+        <v>8.0000000000000007E-5</v>
       </c>
       <c r="AE17" s="1">
-        <v>6.9415595937526701E-6</v>
+        <v>6.973E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:31">
       <c r="A18" s="1">
         <v>0</v>
       </c>
       <c r="B18" s="1">
-        <v>0</v>
+        <v>3.764E-3</v>
       </c>
       <c r="C18" s="1">
-        <v>2.5110044797755006E-6</v>
+        <v>3.5113999999999999E-2</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>6.2927420866218047E-6</v>
+        <v>8.4531999999999996E-2</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>7.5199999999999996E-4</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -2006,13 +2006,13 @@
         <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>2.3395614046516239E-6</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>0</v>
+        <v>1.114E-3</v>
       </c>
       <c r="K18" s="1">
-        <v>3.3674072783069648E-6</v>
+        <v>2.82E-3</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
@@ -2027,25 +2027,25 @@
         <v>0</v>
       </c>
       <c r="P18" s="1">
-        <v>3.3403419232077593E-5</v>
+        <v>0.10491</v>
       </c>
       <c r="Q18" s="1">
-        <v>0</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="R18" s="1">
-        <v>2.034365330100486E-4</v>
+        <v>0.62709499999999996</v>
       </c>
       <c r="S18" s="1">
-        <v>1.6433129132249302E-6</v>
+        <v>6.6090000000000003E-3</v>
       </c>
       <c r="T18" s="1">
-        <v>1.5200846981542479E-6</v>
+        <v>4.2259999999999997E-3</v>
       </c>
       <c r="U18" s="1">
         <v>0</v>
       </c>
       <c r="V18" s="1">
-        <v>2.1639965223621742E-6</v>
+        <v>5.1260000000000003E-3</v>
       </c>
       <c r="W18" s="1">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="Y18" s="1">
-        <v>1.1958453746415284E-4</v>
+        <v>6.5995999999999999E-2</v>
       </c>
       <c r="Z18" s="1">
-        <v>0</v>
+        <v>1.7260000000000001E-3</v>
       </c>
       <c r="AA18" s="1">
         <v>0</v>
@@ -2069,51 +2069,51 @@
         <v>0</v>
       </c>
       <c r="AD18" s="1">
-        <v>3.146456303588084E-5</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="1">
-        <v>9.9637351991960097E-6</v>
+        <v>5.6120999999999997E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:31">
       <c r="A19" s="1">
-        <v>0</v>
+        <v>4.5600000000000003E-4</v>
       </c>
       <c r="B19" s="1">
-        <v>1.3013158943821326E-6</v>
+        <v>6.8799999999999998E-3</v>
       </c>
       <c r="C19" s="1">
-        <v>3.5203220366918923E-7</v>
+        <v>1.008E-3</v>
       </c>
       <c r="D19" s="1">
-        <v>1.0789685589650548E-5</v>
+        <v>2.3466999999999998E-2</v>
       </c>
       <c r="E19" s="1">
-        <v>1.2589928984888759E-6</v>
+        <v>8.3600000000000005E-4</v>
       </c>
       <c r="F19" s="1">
-        <v>1.8288534738542781E-5</v>
+        <v>4.8014000000000001E-2</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>3.4329999999999999E-3</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>5.8699999999999996E-4</v>
       </c>
       <c r="I19" s="1">
-        <v>2.3395614046516239E-6</v>
+        <v>6.4800000000000003E-4</v>
       </c>
       <c r="J19" s="1">
-        <v>0</v>
+        <v>6.1499999999999999E-4</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>1.1313340088519046E-5</v>
+        <v>4.6769999999999997E-3</v>
       </c>
       <c r="M19" s="1">
-        <v>6.3223234920179669E-6</v>
+        <v>3.3799999999999998E-4</v>
       </c>
       <c r="N19" s="1">
         <v>0</v>
@@ -2122,28 +2122,28 @@
         <v>0</v>
       </c>
       <c r="P19" s="1">
-        <v>0</v>
+        <v>7.9699999999999997E-4</v>
       </c>
       <c r="Q19" s="1">
-        <v>4.8051688177230538E-5</v>
+        <v>0.13464799999999999</v>
       </c>
       <c r="R19" s="1">
-        <v>2.3216550543274925E-6</v>
+        <v>3.6189999999999998E-3</v>
       </c>
       <c r="S19" s="1">
-        <v>4.2487681475884191E-4</v>
+        <v>0.64873999999999998</v>
       </c>
       <c r="T19" s="1">
-        <v>3.0401693963084958E-6</v>
+        <v>6.3449999999999999E-3</v>
       </c>
       <c r="U19" s="1">
-        <v>5.6979725867373309E-6</v>
+        <v>4.4689999999999999E-3</v>
       </c>
       <c r="V19" s="1">
-        <v>1.4426643482414495E-6</v>
+        <v>6.3990000000000002E-3</v>
       </c>
       <c r="W19" s="1">
-        <v>2.2916916549976316E-6</v>
+        <v>5.3680000000000004E-3</v>
       </c>
       <c r="X19" s="1">
         <v>0</v>
@@ -2152,25 +2152,25 @@
         <v>0</v>
       </c>
       <c r="Z19" s="1">
-        <v>2.1055369207904789E-4</v>
+        <v>6.6335000000000005E-2</v>
       </c>
       <c r="AA19" s="1">
-        <v>0</v>
+        <v>2.0699999999999998E-3</v>
       </c>
       <c r="AB19" s="1">
-        <v>6.2556824517614903E-6</v>
+        <v>4.2900000000000002E-4</v>
       </c>
       <c r="AC19" s="1">
-        <v>0</v>
+        <v>2.14E-4</v>
       </c>
       <c r="AD19" s="1">
-        <v>0</v>
+        <v>3.4200000000000002E-4</v>
       </c>
       <c r="AE19" s="1">
-        <v>8.1320659216608195E-6</v>
+        <v>2.9269E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:31">
       <c r="A20" s="1">
         <v>0</v>
       </c>
@@ -2178,31 +2178,31 @@
         <v>0</v>
       </c>
       <c r="C20" s="1">
-        <v>5.5156997676996828E-7</v>
+        <v>3.0075999999999999E-2</v>
       </c>
       <c r="D20" s="1">
-        <v>5.1437774661217142E-7</v>
+        <v>2.594E-3</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>3.0599999999999998E-3</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>8.7276332444223984E-6</v>
+        <v>5.4739999999999997E-2</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
       </c>
       <c r="I20" s="1">
-        <v>0</v>
+        <v>6.9090000000000002E-3</v>
       </c>
       <c r="J20" s="1">
         <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>3.5270000000000002E-3</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -2217,28 +2217,28 @@
         <v>0</v>
       </c>
       <c r="P20" s="1">
-        <v>0</v>
+        <v>4.9179999999999996E-3</v>
       </c>
       <c r="Q20" s="1">
-        <v>0</v>
+        <v>4.7749999999999997E-3</v>
       </c>
       <c r="R20" s="1">
-        <v>0</v>
+        <v>2.1800000000000001E-4</v>
       </c>
       <c r="S20" s="1">
-        <v>0</v>
+        <v>4.1850000000000004E-3</v>
       </c>
       <c r="T20" s="1">
-        <v>8.5647523548384064E-5</v>
+        <v>0.60952399999999995</v>
       </c>
       <c r="U20" s="1">
-        <v>0</v>
+        <v>5.1330000000000004E-3</v>
       </c>
       <c r="V20" s="1">
-        <v>2.813767964923303E-5</v>
+        <v>0.23864299999999999</v>
       </c>
       <c r="W20" s="1">
-        <v>0</v>
+        <v>1.9989999999999999E-3</v>
       </c>
       <c r="X20" s="1">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="AA20" s="1">
-        <v>0</v>
+        <v>1.2054E-2</v>
       </c>
       <c r="AB20" s="1">
         <v>0</v>
@@ -2262,33 +2262,33 @@
         <v>0</v>
       </c>
       <c r="AE20" s="1">
-        <v>5.9499082232165745E-7</v>
+        <v>1.7646999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:31">
       <c r="A21" s="1">
         <v>0</v>
       </c>
       <c r="B21" s="1">
-        <v>0</v>
+        <v>5.6099999999999998E-4</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
       </c>
       <c r="D21" s="1">
-        <v>5.1437774661217142E-7</v>
+        <v>1.048E-2</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>7.3239391155516181E-7</v>
+        <v>2.4677000000000001E-2</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>5.6294504813776657E-5</v>
+        <v>8.3580000000000008E-3</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -2315,25 +2315,25 @@
         <v>0</v>
       </c>
       <c r="Q21" s="1">
-        <v>8.0940341771451638E-7</v>
+        <v>0</v>
       </c>
       <c r="R21" s="1">
         <v>0</v>
       </c>
       <c r="S21" s="1">
-        <v>1.2324846849186976E-6</v>
+        <v>1.0911000000000001E-2</v>
       </c>
       <c r="T21" s="1">
-        <v>0</v>
+        <v>3.6422000000000003E-2</v>
       </c>
       <c r="U21" s="1">
-        <v>8.8333649095980832E-5</v>
+        <v>0.57406000000000001</v>
       </c>
       <c r="V21" s="1">
-        <v>0</v>
+        <v>1.5043000000000001E-2</v>
       </c>
       <c r="W21" s="1">
-        <v>6.1887800037607992E-5</v>
+        <v>0.229128</v>
       </c>
       <c r="X21" s="1">
         <v>0</v>
@@ -2348,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="AB21" s="1">
-        <v>0</v>
+        <v>3.411E-3</v>
       </c>
       <c r="AC21" s="1">
         <v>0</v>
@@ -2357,10 +2357,10 @@
         <v>0</v>
       </c>
       <c r="AE21" s="1">
-        <v>1.7849724669649723E-6</v>
+        <v>8.6948999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:31">
       <c r="A22" s="1">
         <v>0</v>
       </c>
@@ -2371,22 +2371,22 @@
         <v>0</v>
       </c>
       <c r="D22" s="1">
-        <v>5.1437774661217142E-7</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>0</v>
+        <v>5.888E-3</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>2.9224E-2</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
       </c>
       <c r="I22" s="1">
-        <v>0</v>
+        <v>8.4611000000000006E-2</v>
       </c>
       <c r="J22" s="1">
         <v>0</v>
@@ -2419,16 +2419,16 @@
         <v>0</v>
       </c>
       <c r="T22" s="1">
-        <v>3.5482047583900302E-6</v>
+        <v>8.8375999999999996E-2</v>
       </c>
       <c r="U22" s="1">
         <v>0</v>
       </c>
       <c r="V22" s="1">
-        <v>2.0201117447730136E-5</v>
+        <v>0.654941</v>
       </c>
       <c r="W22" s="1">
-        <v>2.2916916549976316E-6</v>
+        <v>0</v>
       </c>
       <c r="X22" s="1">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="AA22" s="1">
-        <v>1.8570299741439524E-5</v>
+        <v>8.0354999999999996E-2</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AE22" s="1">
-        <v>3.9666054821443828E-7</v>
+        <v>5.6605000000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:31">
       <c r="A23" s="1">
         <v>0</v>
       </c>
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>6.4854999999999996E-2</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>0</v>
+        <v>8.8178999999999993E-2</v>
       </c>
       <c r="M23" s="1">
         <v>0</v>
@@ -2511,19 +2511,19 @@
         <v>0</v>
       </c>
       <c r="S23" s="1">
-        <v>4.1082822830623254E-7</v>
+        <v>0</v>
       </c>
       <c r="T23" s="1">
         <v>0</v>
       </c>
       <c r="U23" s="1">
-        <v>5.6979725867373309E-6</v>
+        <v>1.6365000000000001E-2</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
       </c>
       <c r="W23" s="1">
-        <v>1.8339595916317023E-5</v>
+        <v>0.43962800000000002</v>
       </c>
       <c r="X23" s="1">
         <v>0</v>
@@ -2547,10 +2547,10 @@
         <v>0</v>
       </c>
       <c r="AE23" s="1">
-        <v>1.3883119187505338E-6</v>
+        <v>0.39097300000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:31">
       <c r="A24" s="1">
         <v>0</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:31">
       <c r="A25" s="1">
         <v>0</v>
       </c>
@@ -2653,13 +2653,13 @@
         <v>0</v>
       </c>
       <c r="C25" s="1">
-        <v>0</v>
+        <v>2.3085999999999999E-2</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>8.389581980221548E-7</v>
+        <v>0.12331300000000001</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>0</v>
+        <v>7.4970000000000002E-3</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -2692,25 +2692,25 @@
         <v>0</v>
       </c>
       <c r="P25" s="1">
-        <v>7.0220127510116167E-7</v>
+        <v>9.5770000000000004E-3</v>
       </c>
       <c r="Q25" s="1">
         <v>0</v>
       </c>
       <c r="R25" s="1">
-        <v>8.2692076285108469E-6</v>
+        <v>0.25576900000000002</v>
       </c>
       <c r="S25" s="1">
         <v>0</v>
       </c>
       <c r="T25" s="1">
-        <v>0</v>
+        <v>1.0477999999999999E-2</v>
       </c>
       <c r="U25" s="1">
         <v>0</v>
       </c>
       <c r="V25" s="1">
-        <v>1.4426643482414495E-6</v>
+        <v>5.3428999999999997E-2</v>
       </c>
       <c r="W25" s="1">
         <v>0</v>
@@ -2719,13 +2719,13 @@
         <v>0</v>
       </c>
       <c r="Y25" s="1">
-        <v>6.9095162715136803E-5</v>
+        <v>0.30515100000000001</v>
       </c>
       <c r="Z25" s="1">
-        <v>0</v>
+        <v>7.8510000000000003E-3</v>
       </c>
       <c r="AA25" s="1">
-        <v>0</v>
+        <v>7.8510000000000003E-3</v>
       </c>
       <c r="AB25" s="1">
         <v>0</v>
@@ -2737,10 +2737,10 @@
         <v>0</v>
       </c>
       <c r="AE25" s="1">
-        <v>3.5704696171947784E-6</v>
+        <v>0.19599900000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:31">
       <c r="A26" s="1">
         <v>0</v>
       </c>
@@ -2748,19 +2748,19 @@
         <v>0</v>
       </c>
       <c r="C26" s="1">
-        <v>0</v>
+        <v>1.9615E-2</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>1.6469000000000001E-2</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="1">
-        <v>2.1952441846349159E-6</v>
+        <v>5.9166999999999997E-2</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>2.3149999999999998E-3</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -2769,19 +2769,19 @@
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>0</v>
+        <v>1.9331000000000001E-2</v>
       </c>
       <c r="K26" s="1">
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>0</v>
+        <v>4.6598000000000001E-2</v>
       </c>
       <c r="M26" s="1">
         <v>0</v>
       </c>
       <c r="N26" s="1">
-        <v>0</v>
+        <v>1.2009000000000001E-2</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -2790,25 +2790,25 @@
         <v>0</v>
       </c>
       <c r="Q26" s="1">
-        <v>5.6764475233118088E-7</v>
+        <v>1.7082E-2</v>
       </c>
       <c r="R26" s="1">
-        <v>0</v>
+        <v>1.7082E-2</v>
       </c>
       <c r="S26" s="1">
-        <v>1.0683707630291709E-5</v>
+        <v>0.31929200000000002</v>
       </c>
       <c r="T26" s="1">
-        <v>1.0133897987694987E-6</v>
+        <v>9.3860000000000002E-3</v>
       </c>
       <c r="U26" s="1">
         <v>0</v>
       </c>
       <c r="V26" s="1">
-        <v>7.2133217412072476E-7</v>
+        <v>8.6160000000000004E-3</v>
       </c>
       <c r="W26" s="1">
-        <v>0</v>
+        <v>2.1457E-2</v>
       </c>
       <c r="X26" s="1">
         <v>0</v>
@@ -2817,13 +2817,13 @@
         <v>0</v>
       </c>
       <c r="Z26" s="1">
-        <v>7.2380278989689649E-5</v>
+        <v>0.28362900000000002</v>
       </c>
       <c r="AA26" s="1">
         <v>0</v>
       </c>
       <c r="AB26" s="1">
-        <v>0</v>
+        <v>7.4669999999999997E-3</v>
       </c>
       <c r="AC26" s="1">
         <v>0</v>
@@ -2832,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="AE26" s="1">
-        <v>2.5788182466586826E-6</v>
+        <v>0.140484</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:31">
       <c r="A27" s="1">
         <v>0</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="AA27" s="1">
-        <v>3.7140599482879054E-6</v>
+        <v>1</v>
       </c>
       <c r="AB27" s="1">
         <v>0</v>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:31">
       <c r="A28" s="1">
         <v>0</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="1">
-        <v>0</v>
+        <v>6.8171999999999996E-2</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
@@ -2989,13 +2989,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="1">
-        <v>0</v>
+        <v>5.3280000000000001E-2</v>
       </c>
       <c r="U28" s="1">
         <v>0</v>
       </c>
       <c r="V28" s="1">
-        <v>0</v>
+        <v>7.7254000000000003E-2</v>
       </c>
       <c r="W28" s="1">
         <v>0</v>
@@ -3013,19 +3013,19 @@
         <v>0</v>
       </c>
       <c r="AB28" s="1">
-        <v>1.2513019845970536E-4</v>
+        <v>0.63758199999999998</v>
       </c>
       <c r="AC28" s="1">
         <v>0</v>
       </c>
       <c r="AD28" s="1">
-        <v>0</v>
+        <v>8.4779999999999994E-2</v>
       </c>
       <c r="AE28" s="1">
-        <v>0</v>
+        <v>7.8932000000000002E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:31">
       <c r="A29" s="1">
         <v>0</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="1">
-        <v>0</v>
+        <v>0.22096099999999999</v>
       </c>
       <c r="N29" s="1">
         <v>0</v>
@@ -3111,16 +3111,16 @@
         <v>0</v>
       </c>
       <c r="AC29" s="1">
-        <v>4.7342744436350815E-5</v>
+        <v>0.44700600000000001</v>
       </c>
       <c r="AD29" s="1">
         <v>0</v>
       </c>
       <c r="AE29" s="1">
-        <v>3.9666054821443828E-7</v>
+        <v>0.33203300000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:31">
       <c r="A30" s="1">
         <v>0</v>
       </c>
@@ -3203,13 +3203,13 @@
         <v>0</v>
       </c>
       <c r="AB30" s="1">
-        <v>6.2556824517614903E-6</v>
+        <v>0</v>
       </c>
       <c r="AC30" s="1">
         <v>0</v>
       </c>
       <c r="AD30" s="1">
-        <v>3.146456303588084E-5</v>
+        <v>0</v>
       </c>
       <c r="AE30" s="1">
         <v>0</v>

--- a/Belle2/data.xlsx
+++ b/Belle2/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwpark\Desktop\git\Belle2_script\Belle2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0BBDE9-F265-428B-B99D-22BABF7A5E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D18B019-9845-4AB4-B98D-1A5E9D8727B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -367,25 +367,25 @@
   <sheetData>
     <row r="1" spans="1:31">
       <c r="A1" s="1">
-        <v>0.70319299999999996</v>
+        <v>12.040509999999999</v>
       </c>
       <c r="B1" s="1">
-        <v>0.20138800000000001</v>
+        <v>3.4387840000000001</v>
       </c>
       <c r="C1" s="1">
-        <v>1.0593E-2</v>
+        <v>0.179115</v>
       </c>
       <c r="D1" s="1">
-        <v>4.2209999999999999E-3</v>
+        <v>7.2114999999999999E-2</v>
       </c>
       <c r="E1" s="1">
-        <v>1.913E-3</v>
+        <v>3.3653000000000002E-2</v>
       </c>
       <c r="F1" s="1">
-        <v>3.2269999999999998E-3</v>
+        <v>5.5481000000000003E-2</v>
       </c>
       <c r="G1" s="1">
-        <v>6.0999999999999999E-5</v>
+        <v>1.036E-3</v>
       </c>
       <c r="H1" s="1">
         <v>0</v>
@@ -394,46 +394,46 @@
         <v>0</v>
       </c>
       <c r="J1" s="1">
-        <v>6.8139999999999997E-3</v>
+        <v>0.119711</v>
       </c>
       <c r="K1" s="1">
-        <v>6.8999999999999997E-5</v>
+        <v>1.1789999999999999E-3</v>
       </c>
       <c r="L1" s="1">
-        <v>3.2899999999999997E-4</v>
+        <v>5.633E-3</v>
       </c>
       <c r="M1" s="1">
-        <v>1.3999999999999999E-4</v>
+        <v>2.3869999999999998E-3</v>
       </c>
       <c r="N1" s="1">
-        <v>2.0999999999999999E-5</v>
+        <v>3.5199999999999999E-4</v>
       </c>
       <c r="O1" s="1">
         <v>0</v>
       </c>
       <c r="P1" s="1">
-        <v>7.6000000000000004E-5</v>
+        <v>1.776E-3</v>
       </c>
       <c r="Q1" s="1">
-        <v>3.6422000000000003E-2</v>
+        <v>0.63344999999999996</v>
       </c>
       <c r="R1" s="1">
-        <v>1.9799999999999999E-4</v>
+        <v>3.4359999999999998E-3</v>
       </c>
       <c r="S1" s="1">
-        <v>6.3990000000000002E-3</v>
+        <v>0.112136</v>
       </c>
       <c r="T1" s="1">
-        <v>1.9599999999999999E-4</v>
+        <v>3.4020000000000001E-3</v>
       </c>
       <c r="U1" s="1">
-        <v>2.9700000000000001E-4</v>
+        <v>4.1229999999999999E-3</v>
       </c>
       <c r="V1" s="1">
-        <v>1.3100000000000001E-4</v>
+        <v>1.836E-3</v>
       </c>
       <c r="W1" s="1">
-        <v>2.0999999999999999E-5</v>
+        <v>3.6600000000000001E-4</v>
       </c>
       <c r="X1" s="1">
         <v>0</v>
@@ -442,42 +442,42 @@
         <v>0</v>
       </c>
       <c r="Z1" s="1">
-        <v>3.39E-4</v>
+        <v>5.8650000000000004E-3</v>
       </c>
       <c r="AA1" s="1">
         <v>0</v>
       </c>
       <c r="AB1" s="1">
-        <v>7.6000000000000004E-5</v>
+        <v>1.3190000000000001E-3</v>
       </c>
       <c r="AC1" s="1">
         <v>0</v>
       </c>
       <c r="AD1" s="1">
-        <v>1.4E-5</v>
+        <v>2.4000000000000001E-4</v>
       </c>
       <c r="AE1" s="1">
-        <v>2.3859999999999999E-2</v>
+        <v>0.407943</v>
       </c>
     </row>
     <row r="2" spans="1:31">
       <c r="A2" s="1">
-        <v>9.1799000000000006E-2</v>
+        <v>0.38566299999999998</v>
       </c>
       <c r="B2" s="1">
-        <v>0.70426500000000003</v>
+        <v>2.9663110000000001</v>
       </c>
       <c r="C2" s="1">
-        <v>1.1421000000000001E-2</v>
+        <v>4.5406000000000002E-2</v>
       </c>
       <c r="D2" s="1">
-        <v>3.7959999999999999E-3</v>
+        <v>1.6469999999999999E-2</v>
       </c>
       <c r="E2" s="1">
-        <v>7.7349999999999997E-3</v>
+        <v>3.3313000000000002E-2</v>
       </c>
       <c r="F2" s="1">
-        <v>1.0496E-2</v>
+        <v>4.5323000000000002E-2</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -486,49 +486,49 @@
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>6.8999999999999997E-5</v>
+        <v>2.9E-4</v>
       </c>
       <c r="J2" s="1">
-        <v>6.4408000000000007E-2</v>
+        <v>0.26583899999999999</v>
       </c>
       <c r="K2" s="1">
-        <v>2.7999999999999998E-4</v>
+        <v>1.232E-3</v>
       </c>
       <c r="L2" s="1">
-        <v>1.0300000000000001E-3</v>
+        <v>5.5180000000000003E-3</v>
       </c>
       <c r="M2" s="1">
-        <v>3.2200000000000002E-4</v>
+        <v>9.810000000000001E-4</v>
       </c>
       <c r="N2" s="1">
-        <v>1.3899999999999999E-4</v>
+        <v>3.5199999999999999E-4</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
       </c>
       <c r="P2" s="1">
-        <v>1.03E-4</v>
+        <v>4.4099999999999999E-4</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.8183999999999999E-2</v>
+        <v>7.6303999999999997E-2</v>
       </c>
       <c r="R2" s="1">
-        <v>2.12E-4</v>
+        <v>8.7500000000000002E-4</v>
       </c>
       <c r="S2" s="1">
-        <v>3.0817000000000001E-2</v>
+        <v>0.13201499999999999</v>
       </c>
       <c r="T2" s="1">
-        <v>4.26E-4</v>
+        <v>1.815E-3</v>
       </c>
       <c r="U2" s="1">
         <v>0</v>
       </c>
       <c r="V2" s="1">
-        <v>1.4100000000000001E-4</v>
+        <v>6.0300000000000002E-4</v>
       </c>
       <c r="W2" s="1">
-        <v>6.9999999999999994E-5</v>
+        <v>2.9700000000000001E-4</v>
       </c>
       <c r="X2" s="1">
         <v>0</v>
@@ -537,13 +537,13 @@
         <v>0</v>
       </c>
       <c r="Z2" s="1">
-        <v>2.2599999999999999E-3</v>
+        <v>9.6360000000000005E-3</v>
       </c>
       <c r="AA2" s="1">
-        <v>3.68E-4</v>
+        <v>1.5679999999999999E-3</v>
       </c>
       <c r="AB2" s="1">
-        <v>5.5999999999999999E-5</v>
+        <v>4.8000000000000001E-4</v>
       </c>
       <c r="AC2" s="1">
         <v>0</v>
@@ -552,42 +552,42 @@
         <v>0</v>
       </c>
       <c r="AE2" s="1">
-        <v>5.1602000000000002E-2</v>
+        <v>0.21810299999999999</v>
       </c>
     </row>
     <row r="3" spans="1:31">
       <c r="A3" s="1">
-        <v>7.3300000000000004E-4</v>
+        <v>1.4959999999999999E-3</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
       </c>
       <c r="C3" s="1">
-        <v>0.81957199999999997</v>
+        <v>1.6726510000000001</v>
       </c>
       <c r="D3" s="1">
-        <v>1.4239999999999999E-3</v>
+        <v>2.542E-3</v>
       </c>
       <c r="E3" s="1">
-        <v>0.128917</v>
+        <v>0.26965299999999998</v>
       </c>
       <c r="F3" s="1">
-        <v>6.6799999999999997E-4</v>
+        <v>1.951E-3</v>
       </c>
       <c r="G3" s="1">
-        <v>2.6220000000000002E-3</v>
+        <v>5.3489999999999996E-3</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>4.9299999999999995E-4</v>
+        <v>1.2509999999999999E-3</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>8.1930000000000006E-3</v>
+        <v>1.6374E-2</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -602,25 +602,25 @@
         <v>0</v>
       </c>
       <c r="P3" s="1">
-        <v>3.6679999999999998E-3</v>
+        <v>7.5750000000000001E-3</v>
       </c>
       <c r="Q3" s="1">
-        <v>2.5790000000000001E-3</v>
+        <v>5.326E-3</v>
       </c>
       <c r="R3" s="1">
-        <v>1.913E-3</v>
+        <v>3.9230000000000003E-3</v>
       </c>
       <c r="S3" s="1">
         <v>0</v>
       </c>
       <c r="T3" s="1">
-        <v>1.6268999999999999E-2</v>
+        <v>3.3384999999999998E-2</v>
       </c>
       <c r="U3" s="1">
-        <v>4.9799999999999996E-4</v>
+        <v>1.0280000000000001E-3</v>
       </c>
       <c r="V3" s="1">
-        <v>4.8269999999999997E-3</v>
+        <v>1.0038E-2</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
@@ -629,16 +629,16 @@
         <v>0</v>
       </c>
       <c r="Y3" s="1">
-        <v>3.1700000000000001E-4</v>
+        <v>6.5399999999999996E-4</v>
       </c>
       <c r="Z3" s="1">
         <v>0</v>
       </c>
       <c r="AA3" s="1">
-        <v>8.0199999999999998E-4</v>
+        <v>1.6559999999999999E-3</v>
       </c>
       <c r="AB3" s="1">
-        <v>1.16E-4</v>
+        <v>2.4000000000000001E-4</v>
       </c>
       <c r="AC3" s="1">
         <v>0</v>
@@ -647,36 +647,36 @@
         <v>0</v>
       </c>
       <c r="AE3" s="1">
-        <v>6.3889999999999997E-3</v>
+        <v>1.3403E-2</v>
       </c>
     </row>
     <row r="4" spans="1:31">
       <c r="A4" s="1">
-        <v>3.4299999999999999E-4</v>
+        <v>4.9799999999999996E-4</v>
       </c>
       <c r="B4" s="1">
-        <v>1.9380000000000001E-3</v>
+        <v>2.6819999999999999E-3</v>
       </c>
       <c r="C4" s="1">
-        <v>4.1920000000000004E-3</v>
+        <v>6.0910000000000001E-3</v>
       </c>
       <c r="D4" s="1">
-        <v>0.61865899999999996</v>
+        <v>0.89956100000000006</v>
       </c>
       <c r="E4" s="1">
-        <v>2.5500000000000002E-4</v>
+        <v>3.6999999999999999E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>0.26722000000000001</v>
+        <v>0.38763199999999998</v>
       </c>
       <c r="G4" s="1">
-        <v>2.7039999999999998E-3</v>
+        <v>4.2810000000000001E-3</v>
       </c>
       <c r="H4" s="1">
-        <v>1.214E-3</v>
+        <v>1.4729999999999999E-3</v>
       </c>
       <c r="I4" s="1">
-        <v>0</v>
+        <v>2.4499999999999999E-4</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>1.8742000000000002E-2</v>
+        <v>2.6352E-2</v>
       </c>
       <c r="M4" s="1">
         <v>0</v>
@@ -700,25 +700,25 @@
         <v>0</v>
       </c>
       <c r="Q4" s="1">
-        <v>2.3116999999999999E-2</v>
+        <v>3.4702999999999998E-2</v>
       </c>
       <c r="R4" s="1">
         <v>0</v>
       </c>
       <c r="S4" s="1">
-        <v>9.3550000000000005E-3</v>
+        <v>1.2995E-2</v>
       </c>
       <c r="T4" s="1">
-        <v>1.0870000000000001E-3</v>
+        <v>1.5989999999999999E-3</v>
       </c>
       <c r="U4" s="1">
-        <v>1.8540999999999998E-2</v>
+        <v>2.5392000000000001E-2</v>
       </c>
       <c r="V4" s="1">
-        <v>9.4799999999999995E-4</v>
+        <v>1.3940000000000001E-3</v>
       </c>
       <c r="W4" s="1">
-        <v>4.5890000000000002E-3</v>
+        <v>7.4840000000000002E-3</v>
       </c>
       <c r="X4" s="1">
         <v>0</v>
@@ -727,13 +727,13 @@
         <v>0</v>
       </c>
       <c r="Z4" s="1">
-        <v>8.8900000000000003E-4</v>
+        <v>1.3079999999999999E-3</v>
       </c>
       <c r="AA4" s="1">
         <v>0</v>
       </c>
       <c r="AB4" s="1">
-        <v>2.5999999999999998E-4</v>
+        <v>3.8299999999999999E-4</v>
       </c>
       <c r="AC4" s="1">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="AE4" s="1">
-        <v>2.5947000000000001E-2</v>
+        <v>3.6339999999999997E-2</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -753,34 +753,34 @@
         <v>0</v>
       </c>
       <c r="C5" s="1">
-        <v>0.15640200000000001</v>
+        <v>6.9336999999999996E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>1.6639999999999999E-3</v>
+        <v>8.3299999999999997E-4</v>
       </c>
       <c r="E5" s="1">
-        <v>0.69167199999999995</v>
+        <v>0.30460599999999999</v>
       </c>
       <c r="F5" s="1">
-        <v>1.9710000000000001E-3</v>
+        <v>8.6200000000000003E-4</v>
       </c>
       <c r="G5" s="1">
-        <v>6.7629999999999999E-3</v>
+        <v>2.9580000000000001E-3</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>4.0769999999999999E-3</v>
+        <v>1.431E-3</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>5.4349000000000001E-2</v>
+        <v>2.4698000000000001E-2</v>
       </c>
       <c r="L5" s="1">
-        <v>1.4599999999999999E-3</v>
+        <v>6.38E-4</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
@@ -795,22 +795,22 @@
         <v>0</v>
       </c>
       <c r="Q5" s="1">
-        <v>2.101E-3</v>
+        <v>9.3000000000000005E-4</v>
       </c>
       <c r="R5" s="1">
-        <v>7.5560000000000002E-3</v>
+        <v>3.346E-3</v>
       </c>
       <c r="S5" s="1">
-        <v>8.5300000000000003E-4</v>
+        <v>3.7800000000000003E-4</v>
       </c>
       <c r="T5" s="1">
-        <v>1.0884E-2</v>
+        <v>5.6610000000000002E-3</v>
       </c>
       <c r="U5" s="1">
         <v>0</v>
       </c>
       <c r="V5" s="1">
-        <v>2.6445E-2</v>
+        <v>1.2768E-2</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="Y5" s="1">
-        <v>1.572E-3</v>
+        <v>6.96E-4</v>
       </c>
       <c r="Z5" s="1">
         <v>0</v>
       </c>
       <c r="AA5" s="1">
-        <v>6.4650000000000003E-3</v>
+        <v>2.209E-3</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="AE5" s="1">
-        <v>2.5767000000000002E-2</v>
+        <v>1.1636000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -845,19 +845,19 @@
         <v>0</v>
       </c>
       <c r="B6" s="1">
-        <v>5.04E-4</v>
+        <v>1.34E-4</v>
       </c>
       <c r="C6" s="1">
-        <v>4.5399999999999998E-4</v>
+        <v>1.2E-4</v>
       </c>
       <c r="D6" s="1">
-        <v>0.105518</v>
+        <v>2.8441999999999999E-2</v>
       </c>
       <c r="E6" s="1">
-        <v>5.6509999999999998E-3</v>
+        <v>1.498E-3</v>
       </c>
       <c r="F6" s="1">
-        <v>0.65035200000000004</v>
+        <v>0.17683099999999999</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>2.274E-3</v>
+        <v>6.0300000000000002E-4</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -875,10 +875,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>0.12246700000000001</v>
+        <v>3.2368000000000001E-2</v>
       </c>
       <c r="M6" s="1">
-        <v>1.4090000000000001E-3</v>
+        <v>3.7399999999999998E-4</v>
       </c>
       <c r="N6" s="1">
         <v>0</v>
@@ -890,25 +890,25 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1">
-        <v>3.7200000000000002E-3</v>
+        <v>9.9799999999999997E-4</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>1.7812000000000001E-2</v>
+        <v>4.7800000000000004E-3</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>7.9039999999999996E-3</v>
+        <v>1.181E-3</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>9.8899999999999995E-3</v>
+        <v>2.9510000000000001E-3</v>
       </c>
       <c r="X6" s="1">
         <v>0</v>
@@ -917,10 +917,10 @@
         <v>0</v>
       </c>
       <c r="Z6" s="1">
-        <v>4.4990000000000004E-3</v>
+        <v>1.207E-3</v>
       </c>
       <c r="AA6" s="1">
-        <v>2.4359999999999998E-3</v>
+        <v>6.5399999999999996E-4</v>
       </c>
       <c r="AB6" s="1">
         <v>0</v>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="AE6" s="1">
-        <v>6.5107999999999999E-2</v>
+        <v>1.6930000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="1">
-        <v>1.7874000000000001E-2</v>
+        <v>3.5199999999999999E-4</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0.59576399999999996</v>
+        <v>1.0808E-2</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>0.172628</v>
+        <v>3.398E-3</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="V7" s="1">
-        <v>0.12711900000000001</v>
+        <v>2.5330000000000001E-3</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
       </c>
       <c r="X7" s="1">
-        <v>1.4912E-2</v>
+        <v>2.9700000000000001E-4</v>
       </c>
       <c r="Y7" s="1">
         <v>0</v>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="AE7" s="1">
-        <v>7.1703000000000003E-2</v>
+        <v>1.4159999999999999E-3</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>0.50224800000000003</v>
+        <v>1.7830000000000001E-3</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="AE8" s="1">
-        <v>0.49775200000000003</v>
+        <v>2.1280000000000001E-3</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>0.79491599999999996</v>
+        <v>1.364E-3</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -1217,27 +1217,27 @@
         <v>0</v>
       </c>
       <c r="AE9" s="1">
-        <v>0.20508399999999999</v>
+        <v>3.5199999999999999E-4</v>
       </c>
     </row>
     <row r="10" spans="1:31">
       <c r="A10" s="1">
-        <v>2.274E-2</v>
+        <v>7.5820000000000002E-3</v>
       </c>
       <c r="B10" s="1">
-        <v>0.26078600000000002</v>
+        <v>8.5429000000000005E-2</v>
       </c>
       <c r="C10" s="1">
-        <v>1.5987000000000001E-2</v>
+        <v>5.2100000000000002E-3</v>
       </c>
       <c r="D10" s="1">
-        <v>4.6569999999999997E-3</v>
+        <v>1.083E-3</v>
       </c>
       <c r="E10" s="1">
-        <v>3.4019000000000001E-2</v>
+        <v>1.1342E-2</v>
       </c>
       <c r="F10" s="1">
-        <v>2.3206999999999998E-2</v>
+        <v>8.1679999999999999E-3</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1249,19 +1249,19 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>0.30868800000000002</v>
+        <v>0.101885</v>
       </c>
       <c r="K10" s="1">
-        <v>3.5370000000000002E-3</v>
+        <v>1.1789999999999999E-3</v>
       </c>
       <c r="L10" s="1">
-        <v>9.2820000000000003E-3</v>
+        <v>3.7330000000000002E-3</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>7.0200000000000004E-4</v>
+        <v>2.34E-4</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1">
-        <v>1.3656E-2</v>
+        <v>4.6090000000000002E-3</v>
       </c>
       <c r="R10" s="1">
-        <v>1.186E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="S10" s="1">
-        <v>2.9184000000000002E-2</v>
+        <v>1.021E-2</v>
       </c>
       <c r="T10" s="1">
         <v>0</v>
@@ -1285,19 +1285,19 @@
         <v>0</v>
       </c>
       <c r="V10" s="1">
-        <v>1.3079999999999999E-3</v>
+        <v>4.4099999999999999E-4</v>
       </c>
       <c r="W10" s="1">
-        <v>7.4299999999999995E-4</v>
+        <v>2.5099999999999998E-4</v>
       </c>
       <c r="X10" s="1">
         <v>0</v>
       </c>
       <c r="Y10" s="1">
-        <v>1.9369999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="1">
-        <v>1.3997000000000001E-2</v>
+        <v>4.1710000000000002E-3</v>
       </c>
       <c r="AA10" s="1">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="1">
-        <v>0.25438499999999997</v>
+        <v>8.5537000000000002E-2</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -1323,16 +1323,16 @@
         <v>0</v>
       </c>
       <c r="C11" s="1">
-        <v>5.9242000000000003E-2</v>
+        <v>1.1130000000000001E-3</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>0.37784400000000001</v>
+        <v>7.0990000000000003E-3</v>
       </c>
       <c r="F11" s="1">
-        <v>3.6239E-2</v>
+        <v>6.8099999999999996E-4</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>0.30583100000000002</v>
+        <v>5.7460000000000002E-3</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="1">
-        <v>2.3789000000000001E-2</v>
+        <v>4.5199999999999998E-4</v>
       </c>
       <c r="Q11" s="1">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="1">
-        <v>3.6655E-2</v>
+        <v>6.9700000000000003E-4</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="AA11" s="1">
-        <v>2.9106E-2</v>
+        <v>5.5400000000000002E-4</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="AE11" s="1">
-        <v>0.131295</v>
+        <v>2.4710000000000001E-3</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>0.51047600000000004</v>
+        <v>4.6979999999999999E-3</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>0.20813999999999999</v>
+        <v>1.915E-3</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="U12" s="1">
-        <v>1.2876E-2</v>
+        <v>1.2E-4</v>
       </c>
       <c r="V12" s="1">
         <v>0</v>
@@ -1502,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="AE12" s="1">
-        <v>0.268507</v>
+        <v>2.8319999999999999E-3</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -1510,13 +1510,13 @@
         <v>0</v>
       </c>
       <c r="B13" s="1">
-        <v>2.0999999999999999E-3</v>
+        <v>1.34E-4</v>
       </c>
       <c r="C13" s="1">
         <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>2.0486000000000001E-2</v>
+        <v>1.3029999999999999E-3</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -1543,13 +1543,13 @@
         <v>0</v>
       </c>
       <c r="M13" s="1">
-        <v>0.83040700000000001</v>
+        <v>5.2586000000000001E-2</v>
       </c>
       <c r="N13" s="1">
         <v>0</v>
       </c>
       <c r="O13" s="1">
-        <v>0.10624599999999999</v>
+        <v>6.992E-3</v>
       </c>
       <c r="P13" s="1">
         <v>0</v>
@@ -1591,13 +1591,13 @@
         <v>0</v>
       </c>
       <c r="AC13" s="1">
-        <v>7.4469999999999996E-3</v>
+        <v>7.1900000000000002E-4</v>
       </c>
       <c r="AD13" s="1">
         <v>0</v>
       </c>
       <c r="AE13" s="1">
-        <v>3.3314999999999997E-2</v>
+        <v>1.776E-3</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>1</v>
+        <v>1.639E-3</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -1733,13 +1733,13 @@
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>0.41548499999999999</v>
+        <v>1.1709999999999999E-3</v>
       </c>
       <c r="N15" s="1">
         <v>0</v>
       </c>
       <c r="O15" s="1">
-        <v>0.24929100000000001</v>
+        <v>7.0200000000000004E-4</v>
       </c>
       <c r="P15" s="1">
         <v>0</v>
@@ -1781,30 +1781,30 @@
         <v>0</v>
       </c>
       <c r="AC15" s="1">
-        <v>8.4053000000000003E-2</v>
+        <v>2.4000000000000001E-4</v>
       </c>
       <c r="AD15" s="1">
         <v>0</v>
       </c>
       <c r="AE15" s="1">
-        <v>0.25117200000000001</v>
+        <v>7.1199999999999996E-4</v>
       </c>
     </row>
     <row r="16" spans="1:31">
       <c r="A16" s="1">
-        <v>2.9700000000000001E-4</v>
+        <v>5.1500000000000005E-4</v>
       </c>
       <c r="B16" s="1">
-        <v>5.7200000000000003E-4</v>
+        <v>9.9299999999999996E-4</v>
       </c>
       <c r="C16" s="1">
-        <v>8.4012000000000003E-2</v>
+        <v>0.14453299999999999</v>
       </c>
       <c r="D16" s="1">
-        <v>2.7099999999999997E-4</v>
+        <v>8.3299999999999997E-4</v>
       </c>
       <c r="E16" s="1">
-        <v>9.1739999999999999E-3</v>
+        <v>1.5924000000000001E-2</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1816,13 +1816,13 @@
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>1.6699999999999999E-4</v>
+        <v>2.9E-4</v>
       </c>
       <c r="J16" s="1">
         <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>5.0699999999999996E-4</v>
+        <v>8.8000000000000003E-4</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>
@@ -1831,31 +1831,31 @@
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <v>2.1499999999999999E-4</v>
+        <v>3.7399999999999998E-4</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
       </c>
       <c r="P16" s="1">
-        <v>0.72145000000000004</v>
+        <v>1.262826</v>
       </c>
       <c r="Q16" s="1">
-        <v>2.3040000000000001E-3</v>
+        <v>3.1740000000000002E-3</v>
       </c>
       <c r="R16" s="1">
-        <v>0.150728</v>
+        <v>0.26345000000000002</v>
       </c>
       <c r="S16" s="1">
-        <v>2.05E-4</v>
+        <v>3.6000000000000002E-4</v>
       </c>
       <c r="T16" s="1">
-        <v>4.9290000000000002E-3</v>
+        <v>8.6730000000000002E-3</v>
       </c>
       <c r="U16" s="1">
         <v>0</v>
       </c>
       <c r="V16" s="1">
-        <v>2.2409999999999999E-3</v>
+        <v>3.9379999999999997E-3</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
@@ -1864,16 +1864,16 @@
         <v>0</v>
       </c>
       <c r="Y16" s="1">
-        <v>4.5869999999999999E-3</v>
+        <v>8.7139999999999995E-3</v>
       </c>
       <c r="Z16" s="1">
-        <v>3.7199999999999999E-4</v>
+        <v>6.5399999999999996E-4</v>
       </c>
       <c r="AA16" s="1">
         <v>0</v>
       </c>
       <c r="AB16" s="1">
-        <v>1.36E-4</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="1">
         <v>0</v>
@@ -1882,30 +1882,30 @@
         <v>0</v>
       </c>
       <c r="AE16" s="1">
-        <v>1.7833000000000002E-2</v>
+        <v>3.1327000000000001E-2</v>
       </c>
     </row>
     <row r="17" spans="1:31">
       <c r="A17" s="1">
-        <v>3.4099999999999998E-3</v>
+        <v>1.5657000000000001E-2</v>
       </c>
       <c r="B17" s="1">
-        <v>3.7309999999999999E-3</v>
+        <v>1.7413000000000001E-2</v>
       </c>
       <c r="C17" s="1">
-        <v>1.7110000000000001E-3</v>
+        <v>9.1009999999999997E-3</v>
       </c>
       <c r="D17" s="1">
-        <v>2.4098000000000001E-2</v>
+        <v>0.11409</v>
       </c>
       <c r="E17" s="1">
-        <v>3.9399999999999998E-4</v>
+        <v>1.867E-3</v>
       </c>
       <c r="F17" s="1">
-        <v>1.2599000000000001E-2</v>
+        <v>5.7473000000000003E-2</v>
       </c>
       <c r="G17" s="1">
-        <v>8.1099999999999998E-4</v>
+        <v>3.8440000000000002E-3</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -1914,16 +1914,16 @@
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>3.4099999999999999E-4</v>
+        <v>1.6169999999999999E-3</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
       </c>
       <c r="L17" s="1">
-        <v>6.1899999999999998E-4</v>
+        <v>2.2959999999999999E-3</v>
       </c>
       <c r="M17" s="1">
-        <v>1.4799999999999999E-4</v>
+        <v>7.0200000000000004E-4</v>
       </c>
       <c r="N17" s="1">
         <v>0</v>
@@ -1932,28 +1932,28 @@
         <v>0</v>
       </c>
       <c r="P17" s="1">
-        <v>1.751E-3</v>
+        <v>8.4010000000000005E-3</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.77739800000000003</v>
+        <v>3.7281140000000001</v>
       </c>
       <c r="R17" s="1">
-        <v>2.1100000000000001E-4</v>
+        <v>1.0120000000000001E-3</v>
       </c>
       <c r="S17" s="1">
-        <v>0.14973</v>
+        <v>0.72091000000000005</v>
       </c>
       <c r="T17" s="1">
-        <v>4.4130000000000003E-3</v>
+        <v>1.9724999999999999E-2</v>
       </c>
       <c r="U17" s="1">
-        <v>1.9919999999999998E-3</v>
+        <v>1.0494E-2</v>
       </c>
       <c r="V17" s="1">
-        <v>9.4499999999999998E-4</v>
+        <v>3.392E-3</v>
       </c>
       <c r="W17" s="1">
-        <v>4.3199999999999998E-4</v>
+        <v>1.7099999999999999E-3</v>
       </c>
       <c r="X17" s="1">
         <v>0</v>
@@ -1962,22 +1962,22 @@
         <v>0</v>
       </c>
       <c r="Z17" s="1">
-        <v>7.5319999999999996E-3</v>
+        <v>3.5478999999999997E-2</v>
       </c>
       <c r="AA17" s="1">
-        <v>1.36E-4</v>
+        <v>6.5399999999999996E-4</v>
       </c>
       <c r="AB17" s="1">
-        <v>3.8499999999999998E-4</v>
+        <v>2.0839999999999999E-3</v>
       </c>
       <c r="AC17" s="1">
-        <v>1.6000000000000001E-4</v>
+        <v>7.6499999999999995E-4</v>
       </c>
       <c r="AD17" s="1">
-        <v>8.0000000000000007E-5</v>
+        <v>3.8299999999999999E-4</v>
       </c>
       <c r="AE17" s="1">
-        <v>6.973E-3</v>
+        <v>3.4812000000000003E-2</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -1985,19 +1985,19 @@
         <v>0</v>
       </c>
       <c r="B18" s="1">
-        <v>3.764E-3</v>
+        <v>2.1580000000000002E-3</v>
       </c>
       <c r="C18" s="1">
-        <v>3.5113999999999999E-2</v>
+        <v>2.0249E-2</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>8.4531999999999996E-2</v>
+        <v>4.8835999999999997E-2</v>
       </c>
       <c r="F18" s="1">
-        <v>7.5199999999999996E-4</v>
+        <v>6.8099999999999996E-4</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -2009,10 +2009,10 @@
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>1.114E-3</v>
+        <v>6.38E-4</v>
       </c>
       <c r="K18" s="1">
-        <v>2.82E-3</v>
+        <v>1.9689999999999998E-3</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
@@ -2027,25 +2027,25 @@
         <v>0</v>
       </c>
       <c r="P18" s="1">
-        <v>0.10491</v>
+        <v>6.0453E-2</v>
       </c>
       <c r="Q18" s="1">
-        <v>9.5000000000000005E-5</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="R18" s="1">
-        <v>0.62709499999999996</v>
+        <v>0.36832500000000001</v>
       </c>
       <c r="S18" s="1">
-        <v>6.6090000000000003E-3</v>
+        <v>3.8349999999999999E-3</v>
       </c>
       <c r="T18" s="1">
-        <v>4.2259999999999997E-3</v>
+        <v>2.4520000000000002E-3</v>
       </c>
       <c r="U18" s="1">
         <v>0</v>
       </c>
       <c r="V18" s="1">
-        <v>5.1260000000000003E-3</v>
+        <v>3.4160000000000002E-3</v>
       </c>
       <c r="W18" s="1">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="Y18" s="1">
-        <v>6.5995999999999999E-2</v>
+        <v>4.0406999999999998E-2</v>
       </c>
       <c r="Z18" s="1">
-        <v>1.7260000000000001E-3</v>
+        <v>3.48E-4</v>
       </c>
       <c r="AA18" s="1">
         <v>0</v>
@@ -2072,48 +2072,48 @@
         <v>0</v>
       </c>
       <c r="AE18" s="1">
-        <v>5.6120999999999997E-2</v>
+        <v>3.2759999999999997E-2</v>
       </c>
     </row>
     <row r="19" spans="1:31">
       <c r="A19" s="1">
-        <v>4.5600000000000003E-4</v>
+        <v>5.0299999999999997E-4</v>
       </c>
       <c r="B19" s="1">
-        <v>6.8799999999999998E-3</v>
+        <v>7.6E-3</v>
       </c>
       <c r="C19" s="1">
-        <v>1.008E-3</v>
+        <v>1.1130000000000001E-3</v>
       </c>
       <c r="D19" s="1">
-        <v>2.3466999999999998E-2</v>
+        <v>2.5922000000000001E-2</v>
       </c>
       <c r="E19" s="1">
-        <v>8.3600000000000005E-4</v>
+        <v>9.2299999999999999E-4</v>
       </c>
       <c r="F19" s="1">
-        <v>4.8014000000000001E-2</v>
+        <v>5.2527999999999998E-2</v>
       </c>
       <c r="G19" s="1">
-        <v>3.4329999999999999E-3</v>
+        <v>3.6749999999999999E-3</v>
       </c>
       <c r="H19" s="1">
-        <v>5.8699999999999996E-4</v>
+        <v>6.4800000000000003E-4</v>
       </c>
       <c r="I19" s="1">
-        <v>6.4800000000000003E-4</v>
+        <v>7.1599999999999995E-4</v>
       </c>
       <c r="J19" s="1">
-        <v>6.1499999999999999E-4</v>
+        <v>6.8000000000000005E-4</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>4.6769999999999997E-3</v>
+        <v>5.8050000000000003E-3</v>
       </c>
       <c r="M19" s="1">
-        <v>3.3799999999999998E-4</v>
+        <v>3.7399999999999998E-4</v>
       </c>
       <c r="N19" s="1">
         <v>0</v>
@@ -2122,28 +2122,28 @@
         <v>0</v>
       </c>
       <c r="P19" s="1">
-        <v>7.9699999999999997E-4</v>
+        <v>8.9099999999999997E-4</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.13464799999999999</v>
+        <v>0.14893999999999999</v>
       </c>
       <c r="R19" s="1">
-        <v>3.6189999999999998E-3</v>
+        <v>4.0480000000000004E-3</v>
       </c>
       <c r="S19" s="1">
-        <v>0.64873999999999998</v>
+        <v>0.71958800000000001</v>
       </c>
       <c r="T19" s="1">
-        <v>6.3449999999999999E-3</v>
+        <v>7.0959999999999999E-3</v>
       </c>
       <c r="U19" s="1">
-        <v>4.4689999999999999E-3</v>
+        <v>4.9969999999999997E-3</v>
       </c>
       <c r="V19" s="1">
-        <v>6.3990000000000002E-3</v>
+        <v>7.156E-3</v>
       </c>
       <c r="W19" s="1">
-        <v>5.3680000000000004E-3</v>
+        <v>6.3E-3</v>
       </c>
       <c r="X19" s="1">
         <v>0</v>
@@ -2152,22 +2152,22 @@
         <v>0</v>
       </c>
       <c r="Z19" s="1">
-        <v>6.6335000000000005E-2</v>
+        <v>7.2568999999999995E-2</v>
       </c>
       <c r="AA19" s="1">
-        <v>2.0699999999999998E-3</v>
+        <v>1.761E-3</v>
       </c>
       <c r="AB19" s="1">
-        <v>4.2900000000000002E-4</v>
+        <v>4.8000000000000001E-4</v>
       </c>
       <c r="AC19" s="1">
-        <v>2.14E-4</v>
+        <v>2.4000000000000001E-4</v>
       </c>
       <c r="AD19" s="1">
-        <v>3.4200000000000002E-4</v>
+        <v>3.8299999999999999E-4</v>
       </c>
       <c r="AE19" s="1">
-        <v>2.9269E-2</v>
+        <v>3.3765000000000003E-2</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -2178,31 +2178,31 @@
         <v>0</v>
       </c>
       <c r="C20" s="1">
-        <v>3.0075999999999999E-2</v>
+        <v>5.4450000000000002E-3</v>
       </c>
       <c r="D20" s="1">
-        <v>2.594E-3</v>
+        <v>4.6999999999999999E-4</v>
       </c>
       <c r="E20" s="1">
-        <v>3.0599999999999998E-3</v>
+        <v>5.5400000000000002E-4</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>5.4739999999999997E-2</v>
+        <v>1.0562E-2</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
       </c>
       <c r="I20" s="1">
-        <v>6.9090000000000002E-3</v>
+        <v>1.2509999999999999E-3</v>
       </c>
       <c r="J20" s="1">
         <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>3.5270000000000002E-3</v>
+        <v>6.38E-4</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -2217,28 +2217,28 @@
         <v>0</v>
       </c>
       <c r="P20" s="1">
-        <v>4.9179999999999996E-3</v>
+        <v>9.01E-4</v>
       </c>
       <c r="Q20" s="1">
-        <v>4.7749999999999997E-3</v>
+        <v>9.9799999999999997E-4</v>
       </c>
       <c r="R20" s="1">
-        <v>2.1800000000000001E-4</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="S20" s="1">
-        <v>4.1850000000000004E-3</v>
+        <v>7.67E-4</v>
       </c>
       <c r="T20" s="1">
-        <v>0.60952399999999995</v>
+        <v>0.110968</v>
       </c>
       <c r="U20" s="1">
-        <v>5.1330000000000004E-3</v>
+        <v>9.41E-4</v>
       </c>
       <c r="V20" s="1">
-        <v>0.23864299999999999</v>
+        <v>4.1648999999999999E-2</v>
       </c>
       <c r="W20" s="1">
-        <v>1.9989999999999999E-3</v>
+        <v>3.6600000000000001E-4</v>
       </c>
       <c r="X20" s="1">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="AA20" s="1">
-        <v>1.2054E-2</v>
+        <v>2.7629999999999998E-3</v>
       </c>
       <c r="AB20" s="1">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="AE20" s="1">
-        <v>1.7646999999999999E-2</v>
+        <v>2.8739999999999998E-3</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -2270,25 +2270,25 @@
         <v>0</v>
       </c>
       <c r="B21" s="1">
-        <v>5.6099999999999998E-4</v>
+        <v>3.8999999999999999E-5</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
       </c>
       <c r="D21" s="1">
-        <v>1.048E-2</v>
+        <v>7.2800000000000002E-4</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>2.4677000000000001E-2</v>
+        <v>1.714E-3</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>8.3580000000000008E-3</v>
+        <v>5.8E-4</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -2321,19 +2321,19 @@
         <v>0</v>
       </c>
       <c r="S21" s="1">
-        <v>1.0911000000000001E-2</v>
+        <v>7.67E-4</v>
       </c>
       <c r="T21" s="1">
-        <v>3.6422000000000003E-2</v>
+        <v>2.5600000000000002E-3</v>
       </c>
       <c r="U21" s="1">
-        <v>0.57406000000000001</v>
+        <v>4.1175999999999997E-2</v>
       </c>
       <c r="V21" s="1">
-        <v>1.5043000000000001E-2</v>
+        <v>1.057E-3</v>
       </c>
       <c r="W21" s="1">
-        <v>0.229128</v>
+        <v>1.5443999999999999E-2</v>
       </c>
       <c r="X21" s="1">
         <v>0</v>
@@ -2348,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="AB21" s="1">
-        <v>3.411E-3</v>
+        <v>2.4000000000000001E-4</v>
       </c>
       <c r="AC21" s="1">
         <v>0</v>
@@ -2357,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="AE21" s="1">
-        <v>8.6948999999999999E-2</v>
+        <v>5.7390000000000002E-3</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -2374,19 +2374,19 @@
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>5.888E-3</v>
+        <v>1.85E-4</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>2.9224E-2</v>
+        <v>9.19E-4</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
       </c>
       <c r="I22" s="1">
-        <v>8.4611000000000006E-2</v>
+        <v>2.66E-3</v>
       </c>
       <c r="J22" s="1">
         <v>0</v>
@@ -2419,13 +2419,13 @@
         <v>0</v>
       </c>
       <c r="T22" s="1">
-        <v>8.8375999999999996E-2</v>
+        <v>2.8119999999999998E-3</v>
       </c>
       <c r="U22" s="1">
         <v>0</v>
       </c>
       <c r="V22" s="1">
-        <v>0.654941</v>
+        <v>2.0506E-2</v>
       </c>
       <c r="W22" s="1">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="AA22" s="1">
-        <v>8.0354999999999996E-2</v>
+        <v>2.5569999999999998E-3</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="AE22" s="1">
-        <v>5.6605000000000003E-2</v>
+        <v>1.8010000000000001E-3</v>
       </c>
     </row>
     <row r="23" spans="1:31">
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="1">
-        <v>6.4854999999999996E-2</v>
+        <v>4.6999999999999999E-4</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>8.8178999999999993E-2</v>
+        <v>6.38E-4</v>
       </c>
       <c r="M23" s="1">
         <v>0</v>
@@ -2517,13 +2517,13 @@
         <v>0</v>
       </c>
       <c r="U23" s="1">
-        <v>1.6365000000000001E-2</v>
+        <v>1.2E-4</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
       </c>
       <c r="W23" s="1">
-        <v>0.43962800000000002</v>
+        <v>3.222E-3</v>
       </c>
       <c r="X23" s="1">
         <v>0</v>
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="AE23" s="1">
-        <v>0.39097300000000001</v>
+        <v>2.8479999999999998E-3</v>
       </c>
     </row>
     <row r="24" spans="1:31">
@@ -2653,13 +2653,13 @@
         <v>0</v>
       </c>
       <c r="C25" s="1">
-        <v>2.3085999999999999E-2</v>
+        <v>1.047E-3</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>0.12331300000000001</v>
+        <v>5.5900000000000004E-3</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>7.4970000000000002E-3</v>
+        <v>3.4000000000000002E-4</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -2692,25 +2692,25 @@
         <v>0</v>
       </c>
       <c r="P25" s="1">
-        <v>9.5770000000000004E-3</v>
+        <v>4.4000000000000002E-4</v>
       </c>
       <c r="Q25" s="1">
         <v>0</v>
       </c>
       <c r="R25" s="1">
-        <v>0.25576900000000002</v>
+        <v>1.1873999999999999E-2</v>
       </c>
       <c r="S25" s="1">
         <v>0</v>
       </c>
       <c r="T25" s="1">
-        <v>1.0477999999999999E-2</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="U25" s="1">
         <v>0</v>
       </c>
       <c r="V25" s="1">
-        <v>5.3428999999999997E-2</v>
+        <v>2.4520000000000002E-3</v>
       </c>
       <c r="W25" s="1">
         <v>0</v>
@@ -2719,13 +2719,13 @@
         <v>0</v>
       </c>
       <c r="Y25" s="1">
-        <v>0.30515100000000001</v>
+        <v>1.4657999999999999E-2</v>
       </c>
       <c r="Z25" s="1">
-        <v>7.8510000000000003E-3</v>
+        <v>3.6000000000000002E-4</v>
       </c>
       <c r="AA25" s="1">
-        <v>7.8510000000000003E-3</v>
+        <v>3.6000000000000002E-4</v>
       </c>
       <c r="AB25" s="1">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="AE25" s="1">
-        <v>0.19599900000000001</v>
+        <v>8.6300000000000005E-3</v>
       </c>
     </row>
     <row r="26" spans="1:31">
@@ -2748,40 +2748,40 @@
         <v>0</v>
       </c>
       <c r="C26" s="1">
-        <v>1.9615E-2</v>
+        <v>9.9299999999999996E-4</v>
       </c>
       <c r="D26" s="1">
-        <v>1.6469000000000001E-2</v>
+        <v>8.3299999999999997E-4</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="1">
-        <v>5.9166999999999997E-2</v>
+        <v>2.9940000000000001E-3</v>
       </c>
       <c r="G26" s="1">
-        <v>2.3149999999999998E-3</v>
+        <v>1.17E-4</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
       </c>
       <c r="I26" s="1">
-        <v>0</v>
+        <v>3.5799999999999997E-4</v>
       </c>
       <c r="J26" s="1">
-        <v>1.9331000000000001E-2</v>
+        <v>9.7799999999999992E-4</v>
       </c>
       <c r="K26" s="1">
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>4.6598000000000001E-2</v>
+        <v>2.3579999999999999E-3</v>
       </c>
       <c r="M26" s="1">
         <v>0</v>
       </c>
       <c r="N26" s="1">
-        <v>1.2009000000000001E-2</v>
+        <v>6.0800000000000003E-4</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -2790,25 +2790,25 @@
         <v>0</v>
       </c>
       <c r="Q26" s="1">
-        <v>1.7082E-2</v>
+        <v>8.7500000000000002E-4</v>
       </c>
       <c r="R26" s="1">
-        <v>1.7082E-2</v>
+        <v>8.7500000000000002E-4</v>
       </c>
       <c r="S26" s="1">
-        <v>0.31929200000000002</v>
+        <v>1.6358000000000001E-2</v>
       </c>
       <c r="T26" s="1">
-        <v>9.3860000000000002E-3</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="U26" s="1">
         <v>0</v>
       </c>
       <c r="V26" s="1">
-        <v>8.6160000000000004E-3</v>
+        <v>4.4099999999999999E-4</v>
       </c>
       <c r="W26" s="1">
-        <v>2.1457E-2</v>
+        <v>1.0989999999999999E-3</v>
       </c>
       <c r="X26" s="1">
         <v>0</v>
@@ -2817,13 +2817,13 @@
         <v>0</v>
       </c>
       <c r="Z26" s="1">
-        <v>0.28362900000000002</v>
+        <v>1.4531000000000001E-2</v>
       </c>
       <c r="AA26" s="1">
         <v>0</v>
       </c>
       <c r="AB26" s="1">
-        <v>7.4669999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="AC26" s="1">
         <v>0</v>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="AE26" s="1">
-        <v>0.140484</v>
+        <v>7.8919999999999997E-3</v>
       </c>
     </row>
     <row r="27" spans="1:31">
@@ -2915,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="AA27" s="1">
-        <v>1</v>
+        <v>6.5399999999999996E-4</v>
       </c>
       <c r="AB27" s="1">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="1">
-        <v>6.8171999999999996E-2</v>
+        <v>6.0800000000000003E-4</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
@@ -2989,13 +2989,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="1">
-        <v>5.3280000000000001E-2</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="U28" s="1">
         <v>0</v>
       </c>
       <c r="V28" s="1">
-        <v>7.7254000000000003E-2</v>
+        <v>6.9700000000000003E-4</v>
       </c>
       <c r="W28" s="1">
         <v>0</v>
@@ -3013,16 +3013,16 @@
         <v>0</v>
       </c>
       <c r="AB28" s="1">
-        <v>0.63758199999999998</v>
+        <v>5.7540000000000004E-3</v>
       </c>
       <c r="AC28" s="1">
         <v>0</v>
       </c>
       <c r="AD28" s="1">
-        <v>8.4779999999999994E-2</v>
+        <v>7.6499999999999995E-4</v>
       </c>
       <c r="AE28" s="1">
-        <v>7.8932000000000002E-2</v>
+        <v>7.0399999999999998E-4</v>
       </c>
     </row>
     <row r="29" spans="1:31">
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="1">
-        <v>0.22096099999999999</v>
+        <v>2.34E-4</v>
       </c>
       <c r="N29" s="1">
         <v>0</v>
@@ -3111,13 +3111,13 @@
         <v>0</v>
       </c>
       <c r="AC29" s="1">
-        <v>0.44700600000000001</v>
+        <v>4.8000000000000001E-4</v>
       </c>
       <c r="AD29" s="1">
         <v>0</v>
       </c>
       <c r="AE29" s="1">
-        <v>0.33203300000000002</v>
+        <v>3.5199999999999999E-4</v>
       </c>
     </row>
     <row r="30" spans="1:31">
